--- a/Datas/AnimalData.xlsx
+++ b/Datas/AnimalData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
   <si>
     <t>鸡</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -71,6 +71,58 @@
   </si>
   <si>
     <t>企鹅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>animalName</t>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>goodId</t>
+  </si>
+  <si>
+    <t>linkCharacter</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>foods</t>
+  </si>
+  <si>
+    <t>produceCycle</t>
+  </si>
+  <si>
+    <t>product</t>
+  </si>
+  <si>
+    <t>cycleStage</t>
+  </si>
+  <si>
+    <t>GrowthStageStr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>List&lt;int&gt;</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小鸡,0,1,0,0|母鸡,1,1,0,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -396,9 +448,108 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <dimension ref="A2:J4"/>
+  <sheetFormatPr defaultColWidth="12.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="6.5" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="5" max="5" width="5.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4">
+        <v>3000</v>
+      </c>
+      <c r="D4">
+        <v>3000</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1101</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>1001</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Datas/AnimalData.xlsx
+++ b/Datas/AnimalData.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="AnimalData" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
@@ -527,6 +527,9 @@
       <c r="B4">
         <v>3000</v>
       </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
       <c r="D4">
         <v>3000</v>
       </c>

--- a/Datas/AnimalData.xlsx
+++ b/Datas/AnimalData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
   <si>
     <t>鸡</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -123,6 +123,13 @@
   </si>
   <si>
     <t>小鸡,0,1,0,0|母鸡,1,1,0,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>behavior</t>
+  </si>
+  <si>
+    <t>鸡</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -448,15 +455,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:J4"/>
+  <dimension ref="A2:K4"/>
   <sheetFormatPr defaultColWidth="12.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="6.5" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="5" max="5" width="5.75" customWidth="1"/>
+    <col min="6" max="6" width="5.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -470,13 +477,13 @@
         <v>24</v>
       </c>
       <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>25</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
       </c>
       <c r="H2" t="s">
         <v>24</v>
@@ -485,10 +492,13 @@
         <v>24</v>
       </c>
       <c r="J2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -502,25 +512,28 @@
         <v>16</v>
       </c>
       <c r="E3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>18</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>19</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>20</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>21</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -533,22 +546,25 @@
       <c r="D4">
         <v>3000</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4">
         <v>1</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>1101</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>2</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>1001</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>1</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>28</v>
       </c>
     </row>

--- a/Datas/AnimalData.xlsx
+++ b/Datas/AnimalData.xlsx
@@ -19,8 +19,44 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>作者</author>
+  </authors>
+  <commentList>
+    <comment ref="L2" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve"> /// &lt;summary&gt;
+    /// 状态名字/// 第几个状态/// 生长周期/// 产出？？
+   /// &lt;/summary&gt;</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
   <si>
     <t>鸡</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -122,14 +158,18 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>小鸡,0,1,0,0|母鸡,1,1,0,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>behavior</t>
   </si>
   <si>
     <t>鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>productCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小鸡,0,1,0,0|母鸡,1,1,0,1|母鸡,2,100,0,0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -137,7 +177,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,6 +191,19 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -454,16 +507,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:K4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:L4"/>
   <sheetFormatPr defaultColWidth="12.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="6.5" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="6" max="6" width="5.75" customWidth="1"/>
+    <col min="12" max="12" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -495,10 +549,13 @@
         <v>24</v>
       </c>
       <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -512,7 +569,7 @@
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
@@ -527,13 +584,16 @@
         <v>20</v>
       </c>
       <c r="J3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" t="s">
         <v>21</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -547,7 +607,7 @@
         <v>3000</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -564,13 +624,17 @@
       <c r="J4">
         <v>1</v>
       </c>
-      <c r="K4" t="s">
-        <v>28</v>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Datas/AnimalData.xlsx
+++ b/Datas/AnimalData.xlsx
@@ -169,7 +169,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>小鸡,0,1,0,0|母鸡,1,1,0,1|母鸡,2,100,0,0</t>
+    <t>小鸡,0,1,0,3000|母鸡,1,100,0,3001|母鸡,2,100,0,3001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -613,7 +613,7 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1101</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>2</v>

--- a/Datas/AnimalData.xlsx
+++ b/Datas/AnimalData.xlsx
@@ -25,7 +25,7 @@
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="L2" authorId="0" shapeId="0">
+    <comment ref="O2" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -35,9 +35,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve"> /// &lt;summary&gt;
-    /// 状态名字/// 第几个状态/// 生长周期/// 产出？？
-   /// &lt;/summary&gt;</t>
+          <t>状态名字/// 第几个状态/// 生长周期/// 产出？？</t>
         </r>
         <r>
           <rPr>
@@ -56,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
   <si>
     <t>鸡</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -171,6 +169,15 @@
   <si>
     <t>小鸡,0,1,0,3000|母鸡,1,100,0,3001|母鸡,2,100,0,3001</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getFoodEmote</t>
+  </si>
+  <si>
+    <t>hungerEmote</t>
+  </si>
+  <si>
+    <t>productEmote</t>
   </si>
 </sst>
 </file>
@@ -508,16 +515,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:L4"/>
+  <dimension ref="A2:O4"/>
   <sheetFormatPr defaultColWidth="12.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="6.5" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="6" max="6" width="5.75" customWidth="1"/>
-    <col min="12" max="12" width="28" customWidth="1"/>
+    <col min="15" max="15" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -552,10 +559,19 @@
         <v>24</v>
       </c>
       <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -590,10 +606,19 @@
         <v>21</v>
       </c>
       <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -627,7 +652,16 @@
       <c r="K4">
         <v>1</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4">
+        <v>8</v>
+      </c>
+      <c r="M4">
+        <v>24</v>
+      </c>
+      <c r="N4">
+        <v>14</v>
+      </c>
+      <c r="O4" t="s">
         <v>31</v>
       </c>
     </row>

--- a/Datas/AnimalData.xlsx
+++ b/Datas/AnimalData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="AnimalData" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="57">
   <si>
     <t>鸡</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -178,6 +178,94 @@
   </si>
   <si>
     <t>productEmote</t>
+  </si>
+  <si>
+    <t>大象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸡蛋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>羊毛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛奶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尖刺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鹿角</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>象牙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兔耳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马尾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>松鼠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>松果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸭子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸭绒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火烈鸟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炭石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰晶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猪肉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兽皮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>袋鼠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>捕捉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -213,12 +301,24 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -233,8 +333,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -674,10 +776,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:D12"/>
+  <dimension ref="A2:E28"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -685,7 +787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -693,7 +795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -701,7 +803,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -709,7 +811,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -717,7 +819,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -725,24 +827,173 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D12" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B15" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" t="s">
+        <v>53</v>
+      </c>
+      <c r="D28" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/AnimalData.xlsx
+++ b/Datas/AnimalData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="AnimalData" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="83">
   <si>
     <t>鸡</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -152,25 +152,13 @@
     <t>string</t>
   </si>
   <si>
-    <t>鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>behavior</t>
   </si>
   <si>
-    <t>鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>productCount</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>小鸡,0,1,0,3000|母鸡,1,100,0,3001|母鸡,2,100,0,3001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>getFoodEmote</t>
   </si>
   <si>
@@ -265,6 +253,117 @@
   </si>
   <si>
     <t>捕捉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>母鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>袋鼠,0,1,0,3114|袋鼠,1,100,0,3114|袋鼠,2,100,0,3114</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>企鹅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>企鹅,0,1,0,3112|企鹅,1,100,0,3112|企鹅,2,100,0,3112</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大象,0,1,0,3110|大象,1,100,0,3110|大象,2,100,0,3110</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刺猬,0,1,0,3108|刺猬,1,100,0,3108|刺猬,2,100,0,3108</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鹿,0,1,0,3106|鹿,1,100,0,3106鹿,2,100,0,3106</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火烈鸟,0,1,0,3104|火烈鸟,1,100,0,3104|火烈鸟,2,100,0,3104</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>野兔,0,1,0,3102|野兔,1,100,0,3102|野兔,2,100,0,3102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>松鼠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>松鼠,0,1,0,3100|松鼠,1,100,0,3100|松鼠,2,100,0,3100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>家兔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼绵羊,0,1,0,3006|绵羊,1,100,0,3007|绵羊,2,100,0,3007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼猪,0,1,0,3008|猪,1,100,0,3009|猪,2,100,0,3009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼鸡,0,1,0,3000|母鸡,1,100,0,3001|母鸡,2,100,0,3001</t>
+  </si>
+  <si>
+    <t>幼鸭,0,1,0,3002|鸭子,1,100,0,3003|鸭子,2,100,0,3003</t>
+  </si>
+  <si>
+    <t>幼兔,0,1,0,3004|家兔,1,100,0,3005|家兔,2,100,0,3005</t>
+  </si>
+  <si>
+    <t>幼牛,0,1,0,3010|奶牛,1,100,0,3011|奶牛,2,100,0,3011</t>
+  </si>
+  <si>
+    <t>幼马,0,1,0,3013|马,1,100,0,3012|马,2,100,0,3012</t>
+  </si>
+  <si>
+    <t>鸭子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绵羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奶牛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>野兔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火烈鸟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刺猬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>袋鼠</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>鹿</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -272,7 +371,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -299,6 +398,13 @@
       <color indexed="81"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -333,10 +439,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -617,12 +729,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:O4"/>
+  <dimension ref="A2:O18"/>
   <sheetFormatPr defaultColWidth="12.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="6.5" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="6" max="6" width="5.75" customWidth="1"/>
+    <col min="7" max="14" width="12.125" customWidth="1"/>
     <col min="15" max="15" width="28" customWidth="1"/>
   </cols>
   <sheetData>
@@ -687,7 +800,7 @@
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
@@ -702,19 +815,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K3" t="s">
         <v>21</v>
       </c>
       <c r="L3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="N3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>
@@ -722,7 +835,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B4">
         <v>3000</v>
@@ -734,7 +847,7 @@
         <v>3000</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -764,13 +877,672 @@
         <v>14</v>
       </c>
       <c r="O4" t="s">
-        <v>31</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5">
+        <v>3002</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>3002</v>
+      </c>
+      <c r="E5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>1001</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>8</v>
+      </c>
+      <c r="M5">
+        <v>24</v>
+      </c>
+      <c r="N5">
+        <v>14</v>
+      </c>
+      <c r="O5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6">
+        <v>3004</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>3004</v>
+      </c>
+      <c r="E6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>1001</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>8</v>
+      </c>
+      <c r="M6">
+        <v>24</v>
+      </c>
+      <c r="N6">
+        <v>14</v>
+      </c>
+      <c r="O6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7">
+        <v>3006</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>3006</v>
+      </c>
+      <c r="E7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>1001</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>8</v>
+      </c>
+      <c r="M7">
+        <v>24</v>
+      </c>
+      <c r="N7">
+        <v>14</v>
+      </c>
+      <c r="O7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8">
+        <v>3008</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>3008</v>
+      </c>
+      <c r="E8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>100</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8">
+        <v>1001</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>8</v>
+      </c>
+      <c r="M8">
+        <v>24</v>
+      </c>
+      <c r="N8">
+        <v>14</v>
+      </c>
+      <c r="O8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9">
+        <v>3010</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>3010</v>
+      </c>
+      <c r="E9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>100</v>
+      </c>
+      <c r="H9">
+        <v>2</v>
+      </c>
+      <c r="I9">
+        <v>1001</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>8</v>
+      </c>
+      <c r="M9">
+        <v>24</v>
+      </c>
+      <c r="N9">
+        <v>14</v>
+      </c>
+      <c r="O9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10">
+        <v>3012</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>3012</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>100</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+      <c r="I10">
+        <v>1001</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>8</v>
+      </c>
+      <c r="M10">
+        <v>24</v>
+      </c>
+      <c r="N10">
+        <v>14</v>
+      </c>
+      <c r="O10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11">
+        <v>3100</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>3100</v>
+      </c>
+      <c r="E11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>100</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11">
+        <v>1001</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>8</v>
+      </c>
+      <c r="M11">
+        <v>24</v>
+      </c>
+      <c r="N11">
+        <v>14</v>
+      </c>
+      <c r="O11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12">
+        <v>3102</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>3102</v>
+      </c>
+      <c r="E12" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>100</v>
+      </c>
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12">
+        <v>1001</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>8</v>
+      </c>
+      <c r="M12">
+        <v>24</v>
+      </c>
+      <c r="N12">
+        <v>14</v>
+      </c>
+      <c r="O12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13">
+        <v>3104</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>3104</v>
+      </c>
+      <c r="E13" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>100</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13">
+        <v>1001</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>8</v>
+      </c>
+      <c r="M13">
+        <v>24</v>
+      </c>
+      <c r="N13">
+        <v>14</v>
+      </c>
+      <c r="O13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14">
+        <v>3106</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>3106</v>
+      </c>
+      <c r="E14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>100</v>
+      </c>
+      <c r="H14">
+        <v>2</v>
+      </c>
+      <c r="I14">
+        <v>1001</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>8</v>
+      </c>
+      <c r="M14">
+        <v>24</v>
+      </c>
+      <c r="N14">
+        <v>14</v>
+      </c>
+      <c r="O14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15">
+        <v>3108</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>3108</v>
+      </c>
+      <c r="E15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>100</v>
+      </c>
+      <c r="H15">
+        <v>2</v>
+      </c>
+      <c r="I15">
+        <v>1001</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>8</v>
+      </c>
+      <c r="M15">
+        <v>24</v>
+      </c>
+      <c r="N15">
+        <v>14</v>
+      </c>
+      <c r="O15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16">
+        <v>3110</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>3110</v>
+      </c>
+      <c r="E16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>100</v>
+      </c>
+      <c r="H16">
+        <v>2</v>
+      </c>
+      <c r="I16">
+        <v>1001</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>8</v>
+      </c>
+      <c r="M16">
+        <v>24</v>
+      </c>
+      <c r="N16">
+        <v>14</v>
+      </c>
+      <c r="O16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17">
+        <v>3112</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>3112</v>
+      </c>
+      <c r="E17" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>100</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="I17">
+        <v>1001</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>8</v>
+      </c>
+      <c r="M17">
+        <v>24</v>
+      </c>
+      <c r="N17">
+        <v>14</v>
+      </c>
+      <c r="O17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" s="3">
+        <v>3114</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3">
+        <v>3114</v>
+      </c>
+      <c r="E18" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>100</v>
+      </c>
+      <c r="H18">
+        <v>2</v>
+      </c>
+      <c r="I18">
+        <v>1001</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>8</v>
+      </c>
+      <c r="M18">
+        <v>24</v>
+      </c>
+      <c r="N18">
+        <v>14</v>
+      </c>
+      <c r="O18" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -844,13 +1616,13 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -858,10 +1630,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -869,10 +1641,10 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.2">
@@ -880,10 +1652,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.2">
@@ -891,10 +1663,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" t="s">
         <v>52</v>
-      </c>
-      <c r="D18" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.2">
@@ -902,21 +1674,21 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D19" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D20" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.2">
@@ -924,10 +1696,10 @@
         <v>6</v>
       </c>
       <c r="C22" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.2">
@@ -935,43 +1707,43 @@
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.2">
@@ -979,21 +1751,21 @@
         <v>12</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D27" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C28" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" t="s">
         <v>53</v>
-      </c>
-      <c r="D28" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/AnimalData.xlsx
+++ b/Datas/AnimalData.xlsx
@@ -33,6 +33,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>状态名字/// 第几个状态/// 生长周期/// 产出？？</t>
@@ -42,6 +43,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -390,6 +392,7 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -397,6 +400,7 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -407,7 +411,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -426,6 +430,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -439,7 +449,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -449,6 +459,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -928,7 +939,7 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="A6" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B6">

--- a/Datas/AnimalData.xlsx
+++ b/Datas/AnimalData.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="85">
   <si>
     <t>鸡</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -367,6 +367,13 @@
   <si>
     <t>鹿</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>functionIds</t>
+  </si>
+  <si>
+    <t>4,9,10,11</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -449,7 +456,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -460,6 +467,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -740,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:O18"/>
+  <dimension ref="A2:P18"/>
   <sheetFormatPr defaultColWidth="12.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="6.5" customWidth="1"/>
@@ -750,7 +760,7 @@
     <col min="15" max="15" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -796,8 +806,11 @@
       <c r="O2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P2" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -843,8 +856,11 @@
       <c r="O3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P3" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>54</v>
       </c>
@@ -887,11 +903,14 @@
       <c r="N4">
         <v>14</v>
       </c>
-      <c r="O4" t="s">
+      <c r="O4" s="6" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P4" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -934,11 +953,14 @@
       <c r="N5">
         <v>14</v>
       </c>
-      <c r="O5" t="s">
+      <c r="O5" s="6" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P5" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>67</v>
       </c>
@@ -981,11 +1003,14 @@
       <c r="N6">
         <v>14</v>
       </c>
-      <c r="O6" t="s">
+      <c r="O6" s="6" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P6" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>76</v>
       </c>
@@ -1028,11 +1053,14 @@
       <c r="N7">
         <v>14</v>
       </c>
-      <c r="O7" t="s">
+      <c r="O7" s="6" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>55</v>
       </c>
@@ -1075,11 +1103,14 @@
       <c r="N8">
         <v>14</v>
       </c>
-      <c r="O8" t="s">
+      <c r="O8" s="6" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>77</v>
       </c>
@@ -1122,11 +1153,14 @@
       <c r="N9">
         <v>14</v>
       </c>
-      <c r="O9" t="s">
+      <c r="O9" s="6" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -1169,11 +1203,14 @@
       <c r="N10">
         <v>14</v>
       </c>
-      <c r="O10" t="s">
+      <c r="O10" s="6" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>65</v>
       </c>
@@ -1216,11 +1253,14 @@
       <c r="N11">
         <v>14</v>
       </c>
-      <c r="O11" t="s">
+      <c r="O11" s="6" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>78</v>
       </c>
@@ -1263,11 +1303,14 @@
       <c r="N12">
         <v>14</v>
       </c>
-      <c r="O12" t="s">
+      <c r="O12" s="6" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>79</v>
       </c>
@@ -1310,11 +1353,14 @@
       <c r="N13">
         <v>14</v>
       </c>
-      <c r="O13" t="s">
+      <c r="O13" s="6" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>82</v>
       </c>
@@ -1357,11 +1403,14 @@
       <c r="N14">
         <v>14</v>
       </c>
-      <c r="O14" t="s">
+      <c r="O14" s="6" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>80</v>
       </c>
@@ -1404,11 +1453,14 @@
       <c r="N15">
         <v>14</v>
       </c>
-      <c r="O15" t="s">
+      <c r="O15" s="6" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>32</v>
       </c>
@@ -1451,11 +1503,14 @@
       <c r="N16">
         <v>14</v>
       </c>
-      <c r="O16" t="s">
+      <c r="O16" s="6" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>58</v>
       </c>
@@ -1498,11 +1553,14 @@
       <c r="N17">
         <v>14</v>
       </c>
-      <c r="O17" t="s">
+      <c r="O17" s="6" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>81</v>
       </c>
@@ -1545,8 +1603,11 @@
       <c r="N18">
         <v>14</v>
       </c>
-      <c r="O18" t="s">
+      <c r="O18" s="6" t="s">
         <v>57</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/AnimalData.xlsx
+++ b/Datas/AnimalData.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="86">
   <si>
     <t>鸡</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -374,6 +374,10 @@
   <si>
     <t>4,9,10,11</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>猪粪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1719,7 +1723,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>2</v>
       </c>
@@ -1730,9 +1734,9 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
         <v>49</v>
@@ -1740,8 +1744,11 @@
       <c r="D18" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="E18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>1</v>
       </c>
@@ -1752,7 +1759,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
         <v>40</v>
       </c>
@@ -1763,7 +1770,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
@@ -1774,7 +1781,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>10</v>
       </c>
@@ -1785,7 +1792,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
         <v>42</v>
       </c>
@@ -1796,7 +1803,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
         <v>46</v>
       </c>
@@ -1807,7 +1814,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>32</v>
       </c>
@@ -1818,7 +1825,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
@@ -1829,7 +1836,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="s">
         <v>51</v>
       </c>

--- a/Datas/AnimalData.xlsx
+++ b/Datas/AnimalData.xlsx
@@ -25,7 +25,7 @@
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="O2" authorId="0" shapeId="0">
+    <comment ref="N2" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="101">
   <si>
     <t>鸡</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -132,12 +132,6 @@
     <t>produceCycle</t>
   </si>
   <si>
-    <t>product</t>
-  </si>
-  <si>
-    <t>cycleStage</t>
-  </si>
-  <si>
     <t>GrowthStageStr</t>
   </si>
   <si>
@@ -157,10 +151,6 @@
     <t>behavior</t>
   </si>
   <si>
-    <t>productCount</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>getFoodEmote</t>
   </si>
   <si>
@@ -178,46 +168,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>羊毛</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>牛奶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>尖刺</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鹿角</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>象牙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>兔耳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>马</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>马尾</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>松鼠</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>松果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>鸭子</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -230,22 +188,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>炭石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰晶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>猪肉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>兽皮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>袋鼠</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -270,71 +212,16 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>袋鼠,0,1,0,3114|袋鼠,1,100,0,3114|袋鼠,2,100,0,3114</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>企鹅</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>企鹅,0,1,0,3112|企鹅,1,100,0,3112|企鹅,2,100,0,3112</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大象,0,1,0,3110|大象,1,100,0,3110|大象,2,100,0,3110</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刺猬,0,1,0,3108|刺猬,1,100,0,3108|刺猬,2,100,0,3108</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鹿,0,1,0,3106|鹿,1,100,0,3106鹿,2,100,0,3106</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火烈鸟,0,1,0,3104|火烈鸟,1,100,0,3104|火烈鸟,2,100,0,3104</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>野兔,0,1,0,3102|野兔,1,100,0,3102|野兔,2,100,0,3102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>松鼠</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>松鼠,0,1,0,3100|松鼠,1,100,0,3100|松鼠,2,100,0,3100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>家兔</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幼绵羊,0,1,0,3006|绵羊,1,100,0,3007|绵羊,2,100,0,3007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幼猪,0,1,0,3008|猪,1,100,0,3009|猪,2,100,0,3009</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幼鸡,0,1,0,3000|母鸡,1,100,0,3001|母鸡,2,100,0,3001</t>
-  </si>
-  <si>
-    <t>幼鸭,0,1,0,3002|鸭子,1,100,0,3003|鸭子,2,100,0,3003</t>
-  </si>
-  <si>
-    <t>幼兔,0,1,0,3004|家兔,1,100,0,3005|家兔,2,100,0,3005</t>
-  </si>
-  <si>
-    <t>幼牛,0,1,0,3010|奶牛,1,100,0,3011|奶牛,2,100,0,3011</t>
-  </si>
-  <si>
-    <t>幼马,0,1,0,3013|马,1,100,0,3012|马,2,100,0,3012</t>
   </si>
   <si>
     <t>鸭子</t>
@@ -378,12 +265,158 @@
   <si>
     <t>猪粪</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马尾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛奶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猪肉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>羊毛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兔耳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>productCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>productCD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼鸡</t>
+  </si>
+  <si>
+    <t>幼鸭</t>
+  </si>
+  <si>
+    <t>幼兔</t>
+  </si>
+  <si>
+    <t>幼绵羊</t>
+  </si>
+  <si>
+    <t>幼猪</t>
+  </si>
+  <si>
+    <t>幼牛</t>
+  </si>
+  <si>
+    <t>幼马</t>
+  </si>
+  <si>
+    <t>松鼠</t>
+  </si>
+  <si>
+    <t>野兔</t>
+  </si>
+  <si>
+    <t>火烈鸟</t>
+  </si>
+  <si>
+    <t>鹿</t>
+  </si>
+  <si>
+    <t>刺猬</t>
+  </si>
+  <si>
+    <t>大象</t>
+  </si>
+  <si>
+    <t>企鹅</t>
+  </si>
+  <si>
+    <t>袋鼠</t>
+  </si>
+  <si>
+    <t>母鸡</t>
+  </si>
+  <si>
+    <t>鸭子</t>
+  </si>
+  <si>
+    <t>家兔</t>
+  </si>
+  <si>
+    <t>绵羊</t>
+  </si>
+  <si>
+    <t>猪</t>
+  </si>
+  <si>
+    <t>奶牛</t>
+  </si>
+  <si>
+    <t>马</t>
+  </si>
+  <si>
+    <t>幼鸡,5,0,3000|母鸡,95,301,3001|母鸡,100,0,3001</t>
+  </si>
+  <si>
+    <t>幼鸭,5,0,3002|鸭子,95,3007,3003|鸭子,100,0,3003</t>
+  </si>
+  <si>
+    <t>幼兔,6,0,3004|家兔,114,302,3005|家兔,100,0,3005</t>
+  </si>
+  <si>
+    <t>幼绵羊,10,0,3006|绵羊,170,283,3007|绵羊,100,0,3007</t>
+  </si>
+  <si>
+    <t>幼猪,10,0,3008|猪,170,3008,3009|猪,100,0,3009</t>
+  </si>
+  <si>
+    <t>幼牛,10,0,3010|奶牛,230,3006,3011|奶牛,100,0,3011</t>
+  </si>
+  <si>
+    <t>幼马,10,0,3013|马,230,276,3012|马,100,0,3012</t>
+  </si>
+  <si>
+    <t>松鼠,5,0,3100|松鼠,95,235,3100|松鼠,100,0,3100</t>
+  </si>
+  <si>
+    <t>野兔,5,0,3102|野兔,95,302,3102|野兔,100,0,3102</t>
+  </si>
+  <si>
+    <t>火烈鸟,6,0,3104|火烈鸟,174,297,3104|火烈鸟,100,0,3104</t>
+  </si>
+  <si>
+    <t>鹿,10,0,3106|鹿,170,222,3106|鹿,100,0,3106</t>
+  </si>
+  <si>
+    <t>刺猬,6,0,3108|刺猬,174,213,3108|刺猬,100,0,3108</t>
+  </si>
+  <si>
+    <t>大象,20,0,3110|大象,220,240,3110|大象,100,0,3110</t>
+  </si>
+  <si>
+    <t>企鹅,12,0,3112|企鹅,228,260,3112|企鹅,100,0,3112</t>
+  </si>
+  <si>
+    <t>袋鼠,15,0,3114|袋鼠,225,203,3114|袋鼠,100,0,3114</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -460,7 +493,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -474,6 +507,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -754,67 +791,64 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:P18"/>
+  <dimension ref="A2:O18"/>
   <sheetFormatPr defaultColWidth="12.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="6.5" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="6" max="6" width="5.75" customWidth="1"/>
-    <col min="7" max="14" width="12.125" customWidth="1"/>
-    <col min="15" max="15" width="28" customWidth="1"/>
+    <col min="7" max="13" width="12.125" customWidth="1"/>
+    <col min="14" max="14" width="47.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" t="s">
-        <v>25</v>
-      </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N2" t="s">
         <v>24</v>
       </c>
-      <c r="O2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="O2" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -828,7 +862,7 @@
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
@@ -840,33 +874,30 @@
         <v>19</v>
       </c>
       <c r="I3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" t="s">
         <v>20</v>
       </c>
-      <c r="J3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" t="s">
-        <v>22</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="O3" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>3000</v>
@@ -878,7 +909,7 @@
         <v>3000</v>
       </c>
       <c r="E4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -889,34 +920,31 @@
       <c r="H4">
         <v>2</v>
       </c>
-      <c r="I4">
-        <v>1001</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
+      <c r="I4" s="7">
+        <v>2</v>
+      </c>
+      <c r="J4" s="7">
+        <v>2</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L4">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="M4">
-        <v>24</v>
-      </c>
-      <c r="N4">
         <v>14</v>
       </c>
-      <c r="O4" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="N4" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="B5">
         <v>3002</v>
@@ -928,7 +956,7 @@
         <v>3002</v>
       </c>
       <c r="E5" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -939,34 +967,31 @@
       <c r="H5">
         <v>2</v>
       </c>
-      <c r="I5">
-        <v>1001</v>
-      </c>
-      <c r="J5">
+      <c r="I5" s="7">
         <v>1</v>
       </c>
+      <c r="J5" s="7">
+        <v>1</v>
+      </c>
       <c r="K5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L5">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="M5">
-        <v>24</v>
-      </c>
-      <c r="N5">
         <v>14</v>
       </c>
-      <c r="O5" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="N5" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="B6">
         <v>3004</v>
@@ -978,7 +1003,7 @@
         <v>3004</v>
       </c>
       <c r="E6" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -989,34 +1014,31 @@
       <c r="H6">
         <v>2</v>
       </c>
-      <c r="I6">
-        <v>1001</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
+      <c r="I6" s="7">
+        <v>2</v>
+      </c>
+      <c r="J6" s="7">
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="M6">
-        <v>24</v>
-      </c>
-      <c r="N6">
         <v>14</v>
       </c>
-      <c r="O6" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="N6" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="B7">
         <v>3006</v>
@@ -1028,7 +1050,7 @@
         <v>3006</v>
       </c>
       <c r="E7" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -1039,34 +1061,31 @@
       <c r="H7">
         <v>2</v>
       </c>
-      <c r="I7">
-        <v>1001</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
+      <c r="I7" s="7">
+        <v>7</v>
+      </c>
+      <c r="J7" s="7">
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="M7">
-        <v>24</v>
-      </c>
-      <c r="N7">
         <v>14</v>
       </c>
-      <c r="O7" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="N7" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <v>3008</v>
@@ -1078,7 +1097,7 @@
         <v>3008</v>
       </c>
       <c r="E8" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1089,34 +1108,31 @@
       <c r="H8">
         <v>2</v>
       </c>
-      <c r="I8">
-        <v>1001</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
+      <c r="I8" s="7">
+        <v>4</v>
+      </c>
+      <c r="J8" s="7">
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="M8">
-        <v>24</v>
-      </c>
-      <c r="N8">
         <v>14</v>
       </c>
-      <c r="O8" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="N8" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="B9">
         <v>3010</v>
@@ -1128,7 +1144,7 @@
         <v>3010</v>
       </c>
       <c r="E9" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1139,34 +1155,31 @@
       <c r="H9">
         <v>2</v>
       </c>
-      <c r="I9">
-        <v>1001</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
+      <c r="I9" s="7">
+        <v>4</v>
+      </c>
+      <c r="J9" s="7">
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="M9">
-        <v>24</v>
-      </c>
-      <c r="N9">
         <v>14</v>
       </c>
-      <c r="O9" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="N9" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B10">
         <v>3012</v>
@@ -1178,7 +1191,7 @@
         <v>3012</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -1189,34 +1202,31 @@
       <c r="H10">
         <v>2</v>
       </c>
-      <c r="I10">
-        <v>1001</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
+      <c r="I10" s="7">
+        <v>3</v>
+      </c>
+      <c r="J10" s="7">
+        <v>4</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="M10">
-        <v>24</v>
-      </c>
-      <c r="N10">
         <v>14</v>
       </c>
-      <c r="O10" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="N10" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>3100</v>
@@ -1228,7 +1238,7 @@
         <v>3100</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -1239,34 +1249,31 @@
       <c r="H11">
         <v>2</v>
       </c>
-      <c r="I11">
-        <v>1001</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
+      <c r="I11" s="7">
+        <v>3</v>
+      </c>
+      <c r="J11" s="7">
+        <v>4</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="M11">
-        <v>24</v>
-      </c>
-      <c r="N11">
         <v>14</v>
       </c>
-      <c r="O11" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="N11" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="B12">
         <v>3102</v>
@@ -1278,7 +1285,7 @@
         <v>3102</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -1289,34 +1296,31 @@
       <c r="H12">
         <v>2</v>
       </c>
-      <c r="I12">
-        <v>1001</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
+      <c r="I12" s="7">
+        <v>2</v>
+      </c>
+      <c r="J12" s="7">
+        <v>3</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="M12">
-        <v>24</v>
-      </c>
-      <c r="N12">
         <v>14</v>
       </c>
-      <c r="O12" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="N12" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="B13">
         <v>3104</v>
@@ -1328,7 +1332,7 @@
         <v>3104</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1339,34 +1343,31 @@
       <c r="H13">
         <v>2</v>
       </c>
-      <c r="I13">
-        <v>1001</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
+      <c r="I13" s="7">
+        <v>4</v>
+      </c>
+      <c r="J13" s="7">
+        <v>2</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="M13">
-        <v>24</v>
-      </c>
-      <c r="N13">
         <v>14</v>
       </c>
-      <c r="O13" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="N13" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="B14">
         <v>3106</v>
@@ -1378,7 +1379,7 @@
         <v>3106</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1389,34 +1390,31 @@
       <c r="H14">
         <v>2</v>
       </c>
-      <c r="I14">
-        <v>1001</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
+      <c r="I14" s="7">
+        <v>2</v>
+      </c>
+      <c r="J14" s="7">
+        <v>2</v>
       </c>
       <c r="K14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="M14">
-        <v>24</v>
-      </c>
-      <c r="N14">
         <v>14</v>
       </c>
-      <c r="O14" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="N14" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="B15">
         <v>3108</v>
@@ -1428,7 +1426,7 @@
         <v>3108</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1439,34 +1437,31 @@
       <c r="H15">
         <v>2</v>
       </c>
-      <c r="I15">
-        <v>1001</v>
-      </c>
-      <c r="J15">
-        <v>1</v>
+      <c r="I15" s="7">
+        <v>4</v>
+      </c>
+      <c r="J15" s="7">
+        <v>3</v>
       </c>
       <c r="K15">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L15">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="M15">
-        <v>24</v>
-      </c>
-      <c r="N15">
         <v>14</v>
       </c>
-      <c r="O15" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="N15" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B16">
         <v>3110</v>
@@ -1478,7 +1473,7 @@
         <v>3110</v>
       </c>
       <c r="E16" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -1489,34 +1484,31 @@
       <c r="H16">
         <v>2</v>
       </c>
-      <c r="I16">
-        <v>1001</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
+      <c r="I16" s="7">
+        <v>2</v>
+      </c>
+      <c r="J16" s="7">
+        <v>4</v>
       </c>
       <c r="K16">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="M16">
-        <v>24</v>
-      </c>
-      <c r="N16">
         <v>14</v>
       </c>
-      <c r="O16" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="N16" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="B17">
         <v>3112</v>
@@ -1528,7 +1520,7 @@
         <v>3112</v>
       </c>
       <c r="E17" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -1539,34 +1531,31 @@
       <c r="H17">
         <v>2</v>
       </c>
-      <c r="I17">
-        <v>1001</v>
-      </c>
-      <c r="J17">
-        <v>1</v>
+      <c r="I17" s="7">
+        <v>2</v>
+      </c>
+      <c r="J17" s="7">
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="M17">
-        <v>24</v>
-      </c>
-      <c r="N17">
         <v>14</v>
       </c>
-      <c r="O17" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="N17" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="B18" s="3">
         <v>3114</v>
@@ -1578,7 +1567,7 @@
         <v>3114</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -1589,29 +1578,26 @@
       <c r="H18">
         <v>2</v>
       </c>
-      <c r="I18">
-        <v>1001</v>
-      </c>
-      <c r="J18">
+      <c r="I18" s="7">
         <v>1</v>
       </c>
+      <c r="J18" s="7">
+        <v>1</v>
+      </c>
       <c r="K18">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="M18">
-        <v>24</v>
-      </c>
-      <c r="N18">
         <v>14</v>
       </c>
-      <c r="O18" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>84</v>
+      <c r="N18" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1624,10 +1610,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:E28"/>
+  <dimension ref="A2:X43"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="11" max="11" width="10.75" customWidth="1"/>
+    <col min="12" max="13" width="7.25" customWidth="1"/>
+    <col min="14" max="14" width="20.625" customWidth="1"/>
+    <col min="15" max="15" width="7.25" customWidth="1"/>
+    <col min="16" max="16" width="9.75" customWidth="1"/>
+    <col min="17" max="17" width="6.125" customWidth="1"/>
+    <col min="18" max="20" width="7.75" customWidth="1"/>
+    <col min="21" max="21" width="8.25" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1635,7 +1631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1643,7 +1639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1651,7 +1647,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1659,7 +1655,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1667,7 +1663,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1675,176 +1671,1027 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="E13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="I14" s="7">
+        <v>100</v>
+      </c>
+      <c r="K14" t="s">
+        <v>64</v>
+      </c>
+      <c r="L14">
+        <v>5</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>3000</v>
+      </c>
+      <c r="P14" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q14" s="8">
+        <f>I14-L14</f>
+        <v>95</v>
+      </c>
+      <c r="R14">
+        <v>301</v>
+      </c>
+      <c r="S14">
+        <v>3001</v>
+      </c>
+      <c r="U14" t="s">
+        <v>79</v>
+      </c>
+      <c r="V14">
+        <v>100</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>3001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="I15" s="7">
+        <v>100</v>
+      </c>
+      <c r="K15" t="s">
+        <v>65</v>
+      </c>
+      <c r="L15">
+        <v>5</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>3002</v>
+      </c>
+      <c r="P15" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q15" s="8">
+        <f t="shared" ref="Q15:Q28" si="0">I15-L15</f>
+        <v>95</v>
+      </c>
+      <c r="R15">
+        <v>3007</v>
+      </c>
+      <c r="S15">
+        <v>3003</v>
+      </c>
+      <c r="U15" t="s">
+        <v>80</v>
+      </c>
+      <c r="V15">
+        <v>100</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>3003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="I16" s="7">
+        <v>120</v>
+      </c>
+      <c r="K16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L16">
+        <v>6</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>3004</v>
+      </c>
+      <c r="P16" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q16" s="8">
+        <f t="shared" si="0"/>
+        <v>114</v>
+      </c>
+      <c r="R16">
+        <v>302</v>
+      </c>
+      <c r="S16">
+        <v>3005</v>
+      </c>
+      <c r="U16" t="s">
+        <v>81</v>
+      </c>
+      <c r="V16">
+        <v>100</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>3005</v>
+      </c>
+    </row>
+    <row r="17" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="I17" s="7">
+        <v>180</v>
+      </c>
+      <c r="K17" t="s">
+        <v>67</v>
+      </c>
+      <c r="L17">
+        <v>10</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>3006</v>
+      </c>
+      <c r="P17" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q17" s="8">
+        <f t="shared" si="0"/>
+        <v>170</v>
+      </c>
+      <c r="R17">
+        <v>283</v>
+      </c>
+      <c r="S17">
+        <v>3007</v>
+      </c>
+      <c r="U17" t="s">
+        <v>82</v>
+      </c>
+      <c r="V17">
+        <v>100</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="18" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" t="s">
         <v>55</v>
       </c>
-      <c r="C18" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="I18" s="7">
+        <v>180</v>
+      </c>
+      <c r="K18" t="s">
+        <v>68</v>
+      </c>
+      <c r="L18">
+        <v>10</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>3008</v>
+      </c>
+      <c r="P18" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q18" s="8">
+        <f t="shared" si="0"/>
+        <v>170</v>
+      </c>
+      <c r="R18">
+        <v>3008</v>
+      </c>
+      <c r="S18">
+        <v>3009</v>
+      </c>
+      <c r="U18" t="s">
+        <v>83</v>
+      </c>
+      <c r="V18">
+        <v>100</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="19" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="I19" s="7">
+        <v>240</v>
+      </c>
+      <c r="K19" t="s">
+        <v>69</v>
+      </c>
+      <c r="L19">
+        <v>10</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>3010</v>
+      </c>
+      <c r="P19" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q19" s="8">
+        <f t="shared" si="0"/>
+        <v>230</v>
+      </c>
+      <c r="R19">
+        <v>3006</v>
+      </c>
+      <c r="S19">
+        <v>3011</v>
+      </c>
+      <c r="U19" t="s">
+        <v>84</v>
+      </c>
+      <c r="V19">
+        <v>100</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>3011</v>
+      </c>
+    </row>
+    <row r="20" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="I20" s="7">
+        <v>240</v>
+      </c>
+      <c r="K20" t="s">
+        <v>70</v>
+      </c>
+      <c r="L20">
+        <v>10</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>3013</v>
+      </c>
+      <c r="P20" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q20" s="8">
+        <f t="shared" si="0"/>
+        <v>230</v>
+      </c>
+      <c r="R20">
+        <v>276</v>
+      </c>
+      <c r="S20">
+        <v>3012</v>
+      </c>
+      <c r="U20" t="s">
+        <v>85</v>
+      </c>
+      <c r="V20">
+        <v>100</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>3012</v>
+      </c>
+    </row>
+    <row r="21" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="I21" s="7">
+        <v>100</v>
+      </c>
+      <c r="K21" t="s">
+        <v>71</v>
+      </c>
+      <c r="L21">
+        <v>5</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>3100</v>
+      </c>
+      <c r="P21" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q21" s="8">
+        <f t="shared" si="0"/>
+        <v>95</v>
+      </c>
+      <c r="R21">
+        <v>235</v>
+      </c>
+      <c r="S21">
+        <v>3100</v>
+      </c>
+      <c r="U21" t="s">
+        <v>71</v>
+      </c>
+      <c r="V21">
+        <v>100</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="22" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C22" t="s">
-        <v>36</v>
-      </c>
       <c r="D22" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+      <c r="I22" s="7">
+        <v>100</v>
+      </c>
+      <c r="K22" t="s">
+        <v>72</v>
+      </c>
+      <c r="L22">
+        <v>5</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>3102</v>
+      </c>
+      <c r="P22" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q22" s="8">
+        <f t="shared" si="0"/>
+        <v>95</v>
+      </c>
+      <c r="R22">
+        <v>302</v>
+      </c>
+      <c r="S22">
+        <v>3102</v>
+      </c>
+      <c r="U22" t="s">
+        <v>72</v>
+      </c>
+      <c r="V22">
+        <v>100</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>3102</v>
+      </c>
+    </row>
+    <row r="23" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C23" t="s">
-        <v>37</v>
-      </c>
       <c r="D23" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+      <c r="I23" s="7">
+        <v>180</v>
+      </c>
+      <c r="K23" t="s">
+        <v>73</v>
+      </c>
+      <c r="L23">
+        <v>6</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>3104</v>
+      </c>
+      <c r="P23" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q23" s="8">
+        <f t="shared" si="0"/>
+        <v>174</v>
+      </c>
+      <c r="R23">
+        <v>297</v>
+      </c>
+      <c r="S23">
+        <v>3104</v>
+      </c>
+      <c r="U23" t="s">
+        <v>73</v>
+      </c>
+      <c r="V23">
+        <v>100</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>3104</v>
+      </c>
+    </row>
+    <row r="24" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D24" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+      <c r="I24" s="7">
+        <v>180</v>
+      </c>
+      <c r="K24" t="s">
+        <v>74</v>
+      </c>
+      <c r="L24">
+        <v>10</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>3106</v>
+      </c>
+      <c r="P24" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q24" s="8">
+        <f t="shared" si="0"/>
+        <v>170</v>
+      </c>
+      <c r="R24">
+        <v>222</v>
+      </c>
+      <c r="S24">
+        <v>3106</v>
+      </c>
+      <c r="U24" t="s">
+        <v>74</v>
+      </c>
+      <c r="V24">
+        <v>100</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>3106</v>
+      </c>
+    </row>
+    <row r="25" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D25" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+      <c r="I25" s="7">
+        <v>180</v>
+      </c>
+      <c r="K25" t="s">
+        <v>75</v>
+      </c>
+      <c r="L25">
+        <v>6</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>3108</v>
+      </c>
+      <c r="P25" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q25" s="8">
+        <f t="shared" si="0"/>
+        <v>174</v>
+      </c>
+      <c r="R25">
+        <v>213</v>
+      </c>
+      <c r="S25">
+        <v>3108</v>
+      </c>
+      <c r="U25" t="s">
+        <v>75</v>
+      </c>
+      <c r="V25">
+        <v>100</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>3108</v>
+      </c>
+    </row>
+    <row r="26" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" t="s">
         <v>38</v>
       </c>
-      <c r="D26" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="I26" s="7">
+        <v>240</v>
+      </c>
+      <c r="K26" t="s">
+        <v>76</v>
+      </c>
+      <c r="L26">
+        <v>20</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>3110</v>
+      </c>
+      <c r="P26" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q26" s="8">
+        <f t="shared" si="0"/>
+        <v>220</v>
+      </c>
+      <c r="R26">
+        <v>240</v>
+      </c>
+      <c r="S26">
+        <v>3110</v>
+      </c>
+      <c r="U26" t="s">
+        <v>76</v>
+      </c>
+      <c r="V26">
+        <v>100</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="27" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C27" t="s">
-        <v>48</v>
-      </c>
       <c r="D27" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+      <c r="I27" s="7">
+        <v>240</v>
+      </c>
+      <c r="K27" t="s">
+        <v>77</v>
+      </c>
+      <c r="L27">
+        <v>12</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>3112</v>
+      </c>
+      <c r="P27" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q27" s="8">
+        <f t="shared" si="0"/>
+        <v>228</v>
+      </c>
+      <c r="R27">
+        <v>260</v>
+      </c>
+      <c r="S27">
+        <v>3112</v>
+      </c>
+      <c r="U27" t="s">
+        <v>77</v>
+      </c>
+      <c r="V27">
+        <v>100</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>3112</v>
+      </c>
+    </row>
+    <row r="28" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D28" t="s">
-        <v>53</v>
+        <v>38</v>
+      </c>
+      <c r="I28" s="7">
+        <v>240</v>
+      </c>
+      <c r="K28" t="s">
+        <v>78</v>
+      </c>
+      <c r="L28">
+        <v>15</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>3114</v>
+      </c>
+      <c r="P28" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q28" s="8">
+        <f t="shared" si="0"/>
+        <v>225</v>
+      </c>
+      <c r="R28">
+        <v>203</v>
+      </c>
+      <c r="S28">
+        <v>3114</v>
+      </c>
+      <c r="U28" t="s">
+        <v>78</v>
+      </c>
+      <c r="V28">
+        <v>100</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>3114</v>
+      </c>
+    </row>
+    <row r="29" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="F29" t="str">
+        <f>N29&amp;"|"&amp;S29&amp;"|"&amp;X29</f>
+        <v>幼鸡,5,0,3000|母鸡,95,301,3001|母鸡,100,0,3001</v>
+      </c>
+      <c r="N29" t="str">
+        <f>K14&amp;","&amp;L14&amp;","&amp;M14&amp;","&amp;N14</f>
+        <v>幼鸡,5,0,3000</v>
+      </c>
+      <c r="S29" t="str">
+        <f>P14&amp;","&amp;Q14&amp;","&amp;R14&amp;","&amp;S14</f>
+        <v>母鸡,95,301,3001</v>
+      </c>
+      <c r="X29" t="str">
+        <f>U14&amp;","&amp;V14&amp;","&amp;W14&amp;","&amp;X14</f>
+        <v>母鸡,100,0,3001</v>
+      </c>
+    </row>
+    <row r="30" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="F30" t="str">
+        <f t="shared" ref="F30:F43" si="1">N30&amp;"|"&amp;S30&amp;"|"&amp;X30</f>
+        <v>幼鸭,5,0,3002|鸭子,95,3007,3003|鸭子,100,0,3003</v>
+      </c>
+      <c r="N30" t="str">
+        <f t="shared" ref="N30:N44" si="2">K15&amp;","&amp;L15&amp;","&amp;M15&amp;","&amp;N15</f>
+        <v>幼鸭,5,0,3002</v>
+      </c>
+      <c r="S30" t="str">
+        <f t="shared" ref="S30:S43" si="3">P15&amp;","&amp;Q15&amp;","&amp;R15&amp;","&amp;S15</f>
+        <v>鸭子,95,3007,3003</v>
+      </c>
+      <c r="X30" t="str">
+        <f t="shared" ref="X30:X43" si="4">U15&amp;","&amp;V15&amp;","&amp;W15&amp;","&amp;X15</f>
+        <v>鸭子,100,0,3003</v>
+      </c>
+    </row>
+    <row r="31" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="F31" t="str">
+        <f t="shared" si="1"/>
+        <v>幼兔,6,0,3004|家兔,114,302,3005|家兔,100,0,3005</v>
+      </c>
+      <c r="N31" t="str">
+        <f t="shared" si="2"/>
+        <v>幼兔,6,0,3004</v>
+      </c>
+      <c r="S31" t="str">
+        <f t="shared" si="3"/>
+        <v>家兔,114,302,3005</v>
+      </c>
+      <c r="X31" t="str">
+        <f t="shared" si="4"/>
+        <v>家兔,100,0,3005</v>
+      </c>
+    </row>
+    <row r="32" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="F32" t="str">
+        <f t="shared" si="1"/>
+        <v>幼绵羊,10,0,3006|绵羊,170,283,3007|绵羊,100,0,3007</v>
+      </c>
+      <c r="N32" t="str">
+        <f t="shared" si="2"/>
+        <v>幼绵羊,10,0,3006</v>
+      </c>
+      <c r="S32" t="str">
+        <f t="shared" si="3"/>
+        <v>绵羊,170,283,3007</v>
+      </c>
+      <c r="X32" t="str">
+        <f t="shared" si="4"/>
+        <v>绵羊,100,0,3007</v>
+      </c>
+    </row>
+    <row r="33" spans="6:24" x14ac:dyDescent="0.2">
+      <c r="F33" t="str">
+        <f t="shared" si="1"/>
+        <v>幼猪,10,0,3008|猪,170,3008,3009|猪,100,0,3009</v>
+      </c>
+      <c r="N33" t="str">
+        <f t="shared" si="2"/>
+        <v>幼猪,10,0,3008</v>
+      </c>
+      <c r="S33" t="str">
+        <f t="shared" si="3"/>
+        <v>猪,170,3008,3009</v>
+      </c>
+      <c r="X33" t="str">
+        <f t="shared" si="4"/>
+        <v>猪,100,0,3009</v>
+      </c>
+    </row>
+    <row r="34" spans="6:24" x14ac:dyDescent="0.2">
+      <c r="F34" t="str">
+        <f t="shared" si="1"/>
+        <v>幼牛,10,0,3010|奶牛,230,3006,3011|奶牛,100,0,3011</v>
+      </c>
+      <c r="N34" t="str">
+        <f t="shared" si="2"/>
+        <v>幼牛,10,0,3010</v>
+      </c>
+      <c r="S34" t="str">
+        <f t="shared" si="3"/>
+        <v>奶牛,230,3006,3011</v>
+      </c>
+      <c r="X34" t="str">
+        <f t="shared" si="4"/>
+        <v>奶牛,100,0,3011</v>
+      </c>
+    </row>
+    <row r="35" spans="6:24" x14ac:dyDescent="0.2">
+      <c r="F35" t="str">
+        <f t="shared" si="1"/>
+        <v>幼马,10,0,3013|马,230,276,3012|马,100,0,3012</v>
+      </c>
+      <c r="N35" t="str">
+        <f t="shared" si="2"/>
+        <v>幼马,10,0,3013</v>
+      </c>
+      <c r="S35" t="str">
+        <f t="shared" si="3"/>
+        <v>马,230,276,3012</v>
+      </c>
+      <c r="X35" t="str">
+        <f t="shared" si="4"/>
+        <v>马,100,0,3012</v>
+      </c>
+    </row>
+    <row r="36" spans="6:24" x14ac:dyDescent="0.2">
+      <c r="F36" t="str">
+        <f t="shared" si="1"/>
+        <v>松鼠,5,0,3100|松鼠,95,235,3100|松鼠,100,0,3100</v>
+      </c>
+      <c r="N36" t="str">
+        <f t="shared" si="2"/>
+        <v>松鼠,5,0,3100</v>
+      </c>
+      <c r="S36" t="str">
+        <f t="shared" si="3"/>
+        <v>松鼠,95,235,3100</v>
+      </c>
+      <c r="X36" t="str">
+        <f t="shared" si="4"/>
+        <v>松鼠,100,0,3100</v>
+      </c>
+    </row>
+    <row r="37" spans="6:24" x14ac:dyDescent="0.2">
+      <c r="F37" t="str">
+        <f t="shared" si="1"/>
+        <v>野兔,5,0,3102|野兔,95,302,3102|野兔,100,0,3102</v>
+      </c>
+      <c r="N37" t="str">
+        <f t="shared" si="2"/>
+        <v>野兔,5,0,3102</v>
+      </c>
+      <c r="S37" t="str">
+        <f t="shared" si="3"/>
+        <v>野兔,95,302,3102</v>
+      </c>
+      <c r="X37" t="str">
+        <f t="shared" si="4"/>
+        <v>野兔,100,0,3102</v>
+      </c>
+    </row>
+    <row r="38" spans="6:24" x14ac:dyDescent="0.2">
+      <c r="F38" t="str">
+        <f t="shared" si="1"/>
+        <v>火烈鸟,6,0,3104|火烈鸟,174,297,3104|火烈鸟,100,0,3104</v>
+      </c>
+      <c r="N38" t="str">
+        <f t="shared" si="2"/>
+        <v>火烈鸟,6,0,3104</v>
+      </c>
+      <c r="S38" t="str">
+        <f t="shared" si="3"/>
+        <v>火烈鸟,174,297,3104</v>
+      </c>
+      <c r="X38" t="str">
+        <f t="shared" si="4"/>
+        <v>火烈鸟,100,0,3104</v>
+      </c>
+    </row>
+    <row r="39" spans="6:24" x14ac:dyDescent="0.2">
+      <c r="F39" t="str">
+        <f t="shared" si="1"/>
+        <v>鹿,10,0,3106|鹿,170,222,3106|鹿,100,0,3106</v>
+      </c>
+      <c r="N39" t="str">
+        <f t="shared" si="2"/>
+        <v>鹿,10,0,3106</v>
+      </c>
+      <c r="S39" t="str">
+        <f t="shared" si="3"/>
+        <v>鹿,170,222,3106</v>
+      </c>
+      <c r="X39" t="str">
+        <f t="shared" si="4"/>
+        <v>鹿,100,0,3106</v>
+      </c>
+    </row>
+    <row r="40" spans="6:24" x14ac:dyDescent="0.2">
+      <c r="F40" t="str">
+        <f t="shared" si="1"/>
+        <v>刺猬,6,0,3108|刺猬,174,213,3108|刺猬,100,0,3108</v>
+      </c>
+      <c r="N40" t="str">
+        <f t="shared" si="2"/>
+        <v>刺猬,6,0,3108</v>
+      </c>
+      <c r="S40" t="str">
+        <f t="shared" si="3"/>
+        <v>刺猬,174,213,3108</v>
+      </c>
+      <c r="X40" t="str">
+        <f t="shared" si="4"/>
+        <v>刺猬,100,0,3108</v>
+      </c>
+    </row>
+    <row r="41" spans="6:24" x14ac:dyDescent="0.2">
+      <c r="F41" t="str">
+        <f t="shared" si="1"/>
+        <v>大象,20,0,3110|大象,220,240,3110|大象,100,0,3110</v>
+      </c>
+      <c r="N41" t="str">
+        <f>K26&amp;","&amp;L26&amp;","&amp;M26&amp;","&amp;N26</f>
+        <v>大象,20,0,3110</v>
+      </c>
+      <c r="S41" t="str">
+        <f>P26&amp;","&amp;Q26&amp;","&amp;R26&amp;","&amp;S26</f>
+        <v>大象,220,240,3110</v>
+      </c>
+      <c r="X41" t="str">
+        <f>U26&amp;","&amp;V26&amp;","&amp;W26&amp;","&amp;X26</f>
+        <v>大象,100,0,3110</v>
+      </c>
+    </row>
+    <row r="42" spans="6:24" x14ac:dyDescent="0.2">
+      <c r="F42" t="str">
+        <f t="shared" si="1"/>
+        <v>企鹅,12,0,3112|企鹅,228,260,3112|企鹅,100,0,3112</v>
+      </c>
+      <c r="N42" t="str">
+        <f t="shared" si="2"/>
+        <v>企鹅,12,0,3112</v>
+      </c>
+      <c r="S42" t="str">
+        <f t="shared" si="3"/>
+        <v>企鹅,228,260,3112</v>
+      </c>
+      <c r="X42" t="str">
+        <f t="shared" si="4"/>
+        <v>企鹅,100,0,3112</v>
+      </c>
+    </row>
+    <row r="43" spans="6:24" x14ac:dyDescent="0.2">
+      <c r="F43" t="str">
+        <f t="shared" si="1"/>
+        <v>袋鼠,15,0,3114|袋鼠,225,203,3114|袋鼠,100,0,3114</v>
+      </c>
+      <c r="N43" t="str">
+        <f t="shared" si="2"/>
+        <v>袋鼠,15,0,3114</v>
+      </c>
+      <c r="S43" t="str">
+        <f t="shared" si="3"/>
+        <v>袋鼠,225,203,3114</v>
+      </c>
+      <c r="X43" t="str">
+        <f t="shared" si="4"/>
+        <v>袋鼠,100,0,3114</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/AnimalData.xlsx
+++ b/Datas/AnimalData.xlsx
@@ -25,7 +25,7 @@
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="N2" authorId="0" shapeId="0">
+    <comment ref="O2" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="119">
   <si>
     <t>鸡</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -168,10 +168,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>马</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>松鼠</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -200,10 +196,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>母鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>猪</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -217,22 +209,6 @@
   </si>
   <si>
     <t>松鼠</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>家兔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鸭子</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>绵羊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奶牛</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -408,6 +384,101 @@
   </si>
   <si>
     <t>袋鼠,15,0,3114|袋鼠,225,203,3114|袋鼠,100,0,3114</t>
+  </si>
+  <si>
+    <t>母鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸭子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>家兔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奶牛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>talkId</t>
+  </si>
+  <si>
+    <t>int2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绵羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8100,8101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8102,8103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8104,8104</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8105,8105</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8106,8106</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8107,8107</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8108,8108</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8109,8109</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8110,8110</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8111,8111</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8112,8112</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8113,8113</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8114,8114</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8115,8115</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8116,8116</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -493,7 +564,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -511,6 +582,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -791,17 +863,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:O18"/>
+  <dimension ref="A2:P18"/>
   <sheetFormatPr defaultColWidth="12.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="6.5" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="6" max="6" width="5.75" customWidth="1"/>
-    <col min="7" max="13" width="12.125" customWidth="1"/>
-    <col min="14" max="14" width="47.875" customWidth="1"/>
+    <col min="7" max="7" width="19.875" style="9" customWidth="1"/>
+    <col min="8" max="14" width="12.125" customWidth="1"/>
+    <col min="15" max="15" width="47.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -820,11 +893,11 @@
       <c r="F2" t="s">
         <v>22</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="H2" t="s">
         <v>23</v>
-      </c>
-      <c r="H2" t="s">
-        <v>22</v>
       </c>
       <c r="I2" t="s">
         <v>22</v>
@@ -842,13 +915,16 @@
         <v>22</v>
       </c>
       <c r="N2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" t="s">
         <v>24</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -867,37 +943,40 @@
       <c r="F3" t="s">
         <v>17</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="H3" t="s">
         <v>18</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>19</v>
       </c>
-      <c r="I3" t="s">
-        <v>62</v>
-      </c>
       <c r="J3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="K3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L3" t="s">
         <v>26</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>27</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>28</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>20</v>
       </c>
-      <c r="O3" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P3" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="B4">
         <v>3000</v>
@@ -909,42 +988,45 @@
         <v>3000</v>
       </c>
       <c r="E4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="G4">
-        <v>100</v>
+      <c r="G4" s="9" t="s">
+        <v>104</v>
       </c>
       <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4" s="7">
+        <v>100</v>
+      </c>
+      <c r="I4">
         <v>2</v>
       </c>
       <c r="J4" s="7">
         <v>2</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="7">
+        <v>2</v>
+      </c>
+      <c r="L4">
         <v>8</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>24</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>14</v>
       </c>
-      <c r="N4" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O4" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="B5">
         <v>3002</v>
@@ -956,42 +1038,45 @@
         <v>3002</v>
       </c>
       <c r="E5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="G5">
-        <v>100</v>
+      <c r="G5" s="9" t="s">
+        <v>105</v>
       </c>
       <c r="H5">
+        <v>100</v>
+      </c>
+      <c r="I5">
         <v>2</v>
-      </c>
-      <c r="I5" s="7">
-        <v>1</v>
       </c>
       <c r="J5" s="7">
         <v>1</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="7">
+        <v>1</v>
+      </c>
+      <c r="L5">
         <v>8</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>24</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>14</v>
       </c>
-      <c r="N5" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O5" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="B6">
         <v>3004</v>
@@ -1003,42 +1088,45 @@
         <v>3004</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6">
-        <v>100</v>
+      <c r="G6" s="9" t="s">
+        <v>106</v>
       </c>
       <c r="H6">
+        <v>100</v>
+      </c>
+      <c r="I6">
         <v>2</v>
       </c>
-      <c r="I6" s="7">
+      <c r="J6" s="7">
         <v>2</v>
       </c>
-      <c r="J6" s="7">
+      <c r="K6" s="7">
         <v>3</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>8</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>24</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>14</v>
       </c>
-      <c r="N6" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O6" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="B7">
         <v>3006</v>
@@ -1050,42 +1138,45 @@
         <v>3006</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
-      <c r="G7">
-        <v>100</v>
+      <c r="G7" s="9" t="s">
+        <v>107</v>
       </c>
       <c r="H7">
+        <v>100</v>
+      </c>
+      <c r="I7">
         <v>2</v>
       </c>
-      <c r="I7" s="7">
+      <c r="J7" s="7">
         <v>7</v>
       </c>
-      <c r="J7" s="7">
+      <c r="K7" s="7">
         <v>4</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>8</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>24</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>14</v>
       </c>
-      <c r="N7" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O7" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="B8">
         <v>3008</v>
@@ -1097,42 +1188,45 @@
         <v>3008</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
-      <c r="G8">
-        <v>100</v>
+      <c r="G8" s="9" t="s">
+        <v>108</v>
       </c>
       <c r="H8">
+        <v>100</v>
+      </c>
+      <c r="I8">
         <v>2</v>
       </c>
-      <c r="I8" s="7">
+      <c r="J8" s="7">
         <v>4</v>
       </c>
-      <c r="J8" s="7">
+      <c r="K8" s="7">
         <v>6</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>8</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>24</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>14</v>
       </c>
-      <c r="N8" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O8" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="B9">
         <v>3010</v>
@@ -1144,42 +1238,45 @@
         <v>3010</v>
       </c>
       <c r="E9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
-      <c r="G9">
-        <v>100</v>
+      <c r="G9" s="9" t="s">
+        <v>109</v>
       </c>
       <c r="H9">
+        <v>100</v>
+      </c>
+      <c r="I9">
         <v>2</v>
-      </c>
-      <c r="I9" s="7">
-        <v>4</v>
       </c>
       <c r="J9" s="7">
         <v>4</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="7">
+        <v>4</v>
+      </c>
+      <c r="L9">
         <v>8</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>24</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>14</v>
       </c>
-      <c r="N9" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="B10">
         <v>3012</v>
@@ -1191,42 +1288,45 @@
         <v>3012</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
-      <c r="G10">
-        <v>100</v>
+      <c r="G10" s="9" t="s">
+        <v>110</v>
       </c>
       <c r="H10">
+        <v>100</v>
+      </c>
+      <c r="I10">
         <v>2</v>
       </c>
-      <c r="I10" s="7">
+      <c r="J10" s="7">
         <v>3</v>
       </c>
-      <c r="J10" s="7">
+      <c r="K10" s="7">
         <v>4</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>8</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>24</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>14</v>
       </c>
-      <c r="N10" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B11">
         <v>3100</v>
@@ -1238,42 +1338,45 @@
         <v>3100</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
-      <c r="G11">
-        <v>100</v>
+      <c r="G11" s="9" t="s">
+        <v>111</v>
       </c>
       <c r="H11">
+        <v>100</v>
+      </c>
+      <c r="I11">
         <v>2</v>
       </c>
-      <c r="I11" s="7">
+      <c r="J11" s="7">
         <v>3</v>
       </c>
-      <c r="J11" s="7">
+      <c r="K11" s="7">
         <v>4</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>8</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>24</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>14</v>
       </c>
-      <c r="N11" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O11" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B12">
         <v>3102</v>
@@ -1285,42 +1388,45 @@
         <v>3102</v>
       </c>
       <c r="E12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
-      <c r="G12">
-        <v>100</v>
+      <c r="G12" s="9" t="s">
+        <v>112</v>
       </c>
       <c r="H12">
+        <v>100</v>
+      </c>
+      <c r="I12">
         <v>2</v>
       </c>
-      <c r="I12" s="7">
+      <c r="J12" s="7">
         <v>2</v>
       </c>
-      <c r="J12" s="7">
+      <c r="K12" s="7">
         <v>3</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>8</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>24</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>14</v>
       </c>
-      <c r="N12" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B13">
         <v>3104</v>
@@ -1332,42 +1438,45 @@
         <v>3104</v>
       </c>
       <c r="E13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
-      <c r="G13">
-        <v>100</v>
+      <c r="G13" s="9" t="s">
+        <v>113</v>
       </c>
       <c r="H13">
+        <v>100</v>
+      </c>
+      <c r="I13">
         <v>2</v>
       </c>
-      <c r="I13" s="7">
+      <c r="J13" s="7">
         <v>4</v>
       </c>
-      <c r="J13" s="7">
+      <c r="K13" s="7">
         <v>2</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>8</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>24</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>14</v>
       </c>
-      <c r="N13" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B14">
         <v>3106</v>
@@ -1379,42 +1488,45 @@
         <v>3106</v>
       </c>
       <c r="E14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
-      <c r="G14">
-        <v>100</v>
+      <c r="G14" s="9" t="s">
+        <v>114</v>
       </c>
       <c r="H14">
-        <v>2</v>
-      </c>
-      <c r="I14" s="7">
+        <v>100</v>
+      </c>
+      <c r="I14">
         <v>2</v>
       </c>
       <c r="J14" s="7">
         <v>2</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="7">
+        <v>2</v>
+      </c>
+      <c r="L14">
         <v>8</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>24</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>14</v>
       </c>
-      <c r="N14" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O14" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B15">
         <v>3108</v>
@@ -1426,40 +1538,43 @@
         <v>3108</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
-      <c r="G15">
-        <v>100</v>
+      <c r="G15" s="9" t="s">
+        <v>115</v>
       </c>
       <c r="H15">
+        <v>100</v>
+      </c>
+      <c r="I15">
         <v>2</v>
       </c>
-      <c r="I15" s="7">
+      <c r="J15" s="7">
         <v>4</v>
       </c>
-      <c r="J15" s="7">
+      <c r="K15" s="7">
         <v>3</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>8</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>24</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>14</v>
       </c>
-      <c r="N15" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>29</v>
       </c>
@@ -1473,42 +1588,45 @@
         <v>3110</v>
       </c>
       <c r="E16" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
-      <c r="G16">
-        <v>100</v>
+      <c r="G16" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="H16">
+        <v>100</v>
+      </c>
+      <c r="I16">
         <v>2</v>
       </c>
-      <c r="I16" s="7">
+      <c r="J16" s="7">
         <v>2</v>
       </c>
-      <c r="J16" s="7">
+      <c r="K16" s="7">
         <v>4</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>8</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>24</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>14</v>
       </c>
-      <c r="N16" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O16" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B17">
         <v>3112</v>
@@ -1520,42 +1638,45 @@
         <v>3112</v>
       </c>
       <c r="E17" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
-      <c r="G17">
-        <v>100</v>
+      <c r="G17" s="9" t="s">
+        <v>117</v>
       </c>
       <c r="H17">
+        <v>100</v>
+      </c>
+      <c r="I17">
         <v>2</v>
       </c>
-      <c r="I17" s="7">
+      <c r="J17" s="7">
         <v>2</v>
       </c>
-      <c r="J17" s="7">
+      <c r="K17" s="7">
         <v>6</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>8</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>24</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>14</v>
       </c>
-      <c r="N17" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B18" s="3">
         <v>3114</v>
@@ -1567,37 +1688,40 @@
         <v>3114</v>
       </c>
       <c r="E18" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
-      <c r="G18">
-        <v>100</v>
+      <c r="G18" s="9" t="s">
+        <v>118</v>
       </c>
       <c r="H18">
+        <v>100</v>
+      </c>
+      <c r="I18">
         <v>2</v>
-      </c>
-      <c r="I18" s="7">
-        <v>1</v>
       </c>
       <c r="J18" s="7">
         <v>1</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="7">
+        <v>1</v>
+      </c>
+      <c r="L18">
         <v>8</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>24</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>14</v>
       </c>
-      <c r="N18" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>54</v>
+      <c r="O18" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1688,19 +1812,19 @@
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
         <v>33</v>
       </c>
-      <c r="C14" t="s">
-        <v>34</v>
-      </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I14" s="7">
         <v>100</v>
       </c>
       <c r="K14" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="L14">
         <v>5</v>
@@ -1712,7 +1836,7 @@
         <v>3000</v>
       </c>
       <c r="P14" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="Q14" s="8">
         <f>I14-L14</f>
@@ -1725,7 +1849,7 @@
         <v>3001</v>
       </c>
       <c r="U14" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -1745,13 +1869,13 @@
         <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I15" s="7">
         <v>100</v>
       </c>
       <c r="K15" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="L15">
         <v>5</v>
@@ -1763,7 +1887,7 @@
         <v>3002</v>
       </c>
       <c r="P15" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="Q15" s="8">
         <f t="shared" ref="Q15:Q28" si="0">I15-L15</f>
@@ -1776,7 +1900,7 @@
         <v>3003</v>
       </c>
       <c r="U15" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="V15">
         <v>100</v>
@@ -1793,16 +1917,16 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I16" s="7">
         <v>120</v>
       </c>
       <c r="K16" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="L16">
         <v>6</v>
@@ -1814,7 +1938,7 @@
         <v>3004</v>
       </c>
       <c r="P16" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="Q16" s="8">
         <f t="shared" si="0"/>
@@ -1827,7 +1951,7 @@
         <v>3005</v>
       </c>
       <c r="U16" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="V16">
         <v>100</v>
@@ -1844,16 +1968,16 @@
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I17" s="7">
         <v>180</v>
       </c>
       <c r="K17" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="L17">
         <v>10</v>
@@ -1865,7 +1989,7 @@
         <v>3006</v>
       </c>
       <c r="P17" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="Q17" s="8">
         <f t="shared" si="0"/>
@@ -1878,7 +2002,7 @@
         <v>3007</v>
       </c>
       <c r="U17" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -1892,22 +2016,22 @@
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E18" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="I18" s="7">
         <v>180</v>
       </c>
       <c r="K18" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="L18">
         <v>10</v>
@@ -1919,7 +2043,7 @@
         <v>3008</v>
       </c>
       <c r="P18" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="Q18" s="8">
         <f t="shared" si="0"/>
@@ -1932,7 +2056,7 @@
         <v>3009</v>
       </c>
       <c r="U18" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -1949,16 +2073,16 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I19" s="7">
         <v>240</v>
       </c>
       <c r="K19" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="L19">
         <v>10</v>
@@ -1970,7 +2094,7 @@
         <v>3010</v>
       </c>
       <c r="P19" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="Q19" s="8">
         <f t="shared" si="0"/>
@@ -1983,7 +2107,7 @@
         <v>3011</v>
       </c>
       <c r="U19" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -1997,19 +2121,19 @@
     </row>
     <row r="20" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I20" s="7">
         <v>240</v>
       </c>
       <c r="K20" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="L20">
         <v>10</v>
@@ -2021,7 +2145,7 @@
         <v>3013</v>
       </c>
       <c r="P20" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="Q20" s="8">
         <f t="shared" si="0"/>
@@ -2034,7 +2158,7 @@
         <v>3012</v>
       </c>
       <c r="U20" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -2051,7 +2175,7 @@
         <v>100</v>
       </c>
       <c r="K21" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="L21">
         <v>5</v>
@@ -2063,7 +2187,7 @@
         <v>3100</v>
       </c>
       <c r="P21" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="Q21" s="8">
         <f t="shared" si="0"/>
@@ -2076,7 +2200,7 @@
         <v>3100</v>
       </c>
       <c r="U21" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -2093,13 +2217,13 @@
         <v>6</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I22" s="7">
         <v>100</v>
       </c>
       <c r="K22" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="L22">
         <v>5</v>
@@ -2111,7 +2235,7 @@
         <v>3102</v>
       </c>
       <c r="P22" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="Q22" s="8">
         <f t="shared" si="0"/>
@@ -2124,7 +2248,7 @@
         <v>3102</v>
       </c>
       <c r="U22" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -2141,13 +2265,13 @@
         <v>10</v>
       </c>
       <c r="D23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I23" s="7">
         <v>180</v>
       </c>
       <c r="K23" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="L23">
         <v>6</v>
@@ -2159,7 +2283,7 @@
         <v>3104</v>
       </c>
       <c r="P23" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="Q23" s="8">
         <f t="shared" si="0"/>
@@ -2172,7 +2296,7 @@
         <v>3104</v>
       </c>
       <c r="U23" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -2186,16 +2310,16 @@
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I24" s="7">
         <v>180</v>
       </c>
       <c r="K24" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="L24">
         <v>10</v>
@@ -2207,7 +2331,7 @@
         <v>3106</v>
       </c>
       <c r="P24" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="Q24" s="8">
         <f t="shared" si="0"/>
@@ -2220,7 +2344,7 @@
         <v>3106</v>
       </c>
       <c r="U24" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -2234,16 +2358,16 @@
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I25" s="7">
         <v>180</v>
       </c>
       <c r="K25" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="L25">
         <v>6</v>
@@ -2255,7 +2379,7 @@
         <v>3108</v>
       </c>
       <c r="P25" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="Q25" s="8">
         <f t="shared" si="0"/>
@@ -2268,7 +2392,7 @@
         <v>3108</v>
       </c>
       <c r="U25" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -2285,13 +2409,13 @@
         <v>29</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I26" s="7">
         <v>240</v>
       </c>
       <c r="K26" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="L26">
         <v>20</v>
@@ -2303,7 +2427,7 @@
         <v>3110</v>
       </c>
       <c r="P26" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="Q26" s="8">
         <f t="shared" si="0"/>
@@ -2316,7 +2440,7 @@
         <v>3110</v>
       </c>
       <c r="U26" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -2333,13 +2457,13 @@
         <v>12</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I27" s="7">
         <v>240</v>
       </c>
       <c r="K27" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="L27">
         <v>12</v>
@@ -2351,7 +2475,7 @@
         <v>3112</v>
       </c>
       <c r="P27" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="Q27" s="8">
         <f t="shared" si="0"/>
@@ -2364,7 +2488,7 @@
         <v>3112</v>
       </c>
       <c r="U27" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="V27">
         <v>100</v>
@@ -2378,16 +2502,16 @@
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I28" s="7">
         <v>240</v>
       </c>
       <c r="K28" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="L28">
         <v>15</v>
@@ -2399,7 +2523,7 @@
         <v>3114</v>
       </c>
       <c r="P28" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="Q28" s="8">
         <f t="shared" si="0"/>
@@ -2412,7 +2536,7 @@
         <v>3114</v>
       </c>
       <c r="U28" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -2448,7 +2572,7 @@
         <v>幼鸭,5,0,3002|鸭子,95,3007,3003|鸭子,100,0,3003</v>
       </c>
       <c r="N30" t="str">
-        <f t="shared" ref="N30:N44" si="2">K15&amp;","&amp;L15&amp;","&amp;M15&amp;","&amp;N15</f>
+        <f t="shared" ref="N30:N43" si="2">K15&amp;","&amp;L15&amp;","&amp;M15&amp;","&amp;N15</f>
         <v>幼鸭,5,0,3002</v>
       </c>
       <c r="S30" t="str">

--- a/Datas/AnimalData.xlsx
+++ b/Datas/AnimalData.xlsx
@@ -25,7 +25,7 @@
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="O2" authorId="0" shapeId="0">
+    <comment ref="P2" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="121">
   <si>
     <t>鸡</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -478,6 +478,14 @@
   </si>
   <si>
     <t>8116,8116</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dailyTasks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20,21,22</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -863,18 +871,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:P18"/>
+  <dimension ref="A2:Q18"/>
   <sheetFormatPr defaultColWidth="12.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="6.5" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="6" max="6" width="5.75" customWidth="1"/>
-    <col min="7" max="7" width="19.875" style="9" customWidth="1"/>
-    <col min="8" max="14" width="12.125" customWidth="1"/>
-    <col min="15" max="15" width="47.875" customWidth="1"/>
+    <col min="7" max="7" width="5.75" customWidth="1"/>
+    <col min="8" max="8" width="19.875" style="9" customWidth="1"/>
+    <col min="9" max="15" width="12.125" customWidth="1"/>
+    <col min="16" max="16" width="47.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -888,19 +896,19 @@
         <v>22</v>
       </c>
       <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
         <v>21</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="H2" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>23</v>
-      </c>
-      <c r="I2" t="s">
-        <v>22</v>
       </c>
       <c r="J2" t="s">
         <v>22</v>
@@ -918,13 +926,16 @@
         <v>22</v>
       </c>
       <c r="O2" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" t="s">
         <v>24</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -938,43 +949,46 @@
         <v>16</v>
       </c>
       <c r="E3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" t="s">
         <v>25</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="H3" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="I3" t="s">
         <v>18</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>19</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>56</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>57</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>26</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>27</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>28</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>20</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>95</v>
       </c>
@@ -988,43 +1002,46 @@
         <v>3000</v>
       </c>
       <c r="E4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F4" t="s">
         <v>39</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>1</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="H4" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="H4">
-        <v>100</v>
-      </c>
       <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4" s="7">
+        <v>100</v>
+      </c>
+      <c r="J4">
         <v>2</v>
       </c>
       <c r="K4" s="7">
         <v>2</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="7">
+        <v>2</v>
+      </c>
+      <c r="M4">
         <v>8</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>24</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>14</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="P4" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="Q4" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>96</v>
       </c>
@@ -1038,43 +1055,46 @@
         <v>3002</v>
       </c>
       <c r="E5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F5" t="s">
         <v>39</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>1</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="H5" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="H5">
-        <v>100</v>
-      </c>
       <c r="I5">
+        <v>100</v>
+      </c>
+      <c r="J5">
         <v>2</v>
-      </c>
-      <c r="J5" s="7">
-        <v>1</v>
       </c>
       <c r="K5" s="7">
         <v>1</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="7">
+        <v>1</v>
+      </c>
+      <c r="M5">
         <v>8</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>24</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>14</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="P5" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="Q5" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>97</v>
       </c>
@@ -1088,43 +1108,46 @@
         <v>3004</v>
       </c>
       <c r="E6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F6" t="s">
         <v>39</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>1</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="H6" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H6">
-        <v>100</v>
-      </c>
       <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6">
         <v>2</v>
       </c>
-      <c r="J6" s="7">
+      <c r="K6" s="7">
         <v>2</v>
       </c>
-      <c r="K6" s="7">
+      <c r="L6" s="7">
         <v>3</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>8</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>24</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>14</v>
       </c>
-      <c r="O6" s="6" t="s">
+      <c r="P6" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="P6" s="3" t="s">
+      <c r="Q6" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>102</v>
       </c>
@@ -1138,43 +1161,46 @@
         <v>3006</v>
       </c>
       <c r="E7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F7" t="s">
         <v>39</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>1</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="H7" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="H7">
-        <v>100</v>
-      </c>
       <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7">
         <v>2</v>
       </c>
-      <c r="J7" s="7">
+      <c r="K7" s="7">
         <v>7</v>
       </c>
-      <c r="K7" s="7">
+      <c r="L7" s="7">
         <v>4</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>8</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>24</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>14</v>
       </c>
-      <c r="O7" s="6" t="s">
+      <c r="P7" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="P7" s="3" t="s">
+      <c r="Q7" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>103</v>
       </c>
@@ -1188,43 +1214,46 @@
         <v>3008</v>
       </c>
       <c r="E8" t="s">
+        <v>120</v>
+      </c>
+      <c r="F8" t="s">
         <v>39</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>1</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="H8" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="H8">
-        <v>100</v>
-      </c>
       <c r="I8">
+        <v>100</v>
+      </c>
+      <c r="J8">
         <v>2</v>
       </c>
-      <c r="J8" s="7">
+      <c r="K8" s="7">
         <v>4</v>
       </c>
-      <c r="K8" s="7">
+      <c r="L8" s="7">
         <v>6</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>8</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>24</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>14</v>
       </c>
-      <c r="O8" s="6" t="s">
+      <c r="P8" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="Q8" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>98</v>
       </c>
@@ -1238,43 +1267,46 @@
         <v>3010</v>
       </c>
       <c r="E9" t="s">
+        <v>120</v>
+      </c>
+      <c r="F9" t="s">
         <v>39</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>1</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="H9" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="H9">
-        <v>100</v>
-      </c>
       <c r="I9">
+        <v>100</v>
+      </c>
+      <c r="J9">
         <v>2</v>
-      </c>
-      <c r="J9" s="7">
-        <v>4</v>
       </c>
       <c r="K9" s="7">
         <v>4</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="7">
+        <v>4</v>
+      </c>
+      <c r="M9">
         <v>8</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>24</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>14</v>
       </c>
-      <c r="O9" s="6" t="s">
+      <c r="P9" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="P9" s="3" t="s">
+      <c r="Q9" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>99</v>
       </c>
@@ -1288,43 +1320,46 @@
         <v>3012</v>
       </c>
       <c r="E10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F10" t="s">
         <v>39</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>1</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="H10" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="H10">
-        <v>100</v>
-      </c>
       <c r="I10">
+        <v>100</v>
+      </c>
+      <c r="J10">
         <v>2</v>
       </c>
-      <c r="J10" s="7">
+      <c r="K10" s="7">
         <v>3</v>
       </c>
-      <c r="K10" s="7">
+      <c r="L10" s="7">
         <v>4</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>8</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>24</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>14</v>
       </c>
-      <c r="O10" s="6" t="s">
+      <c r="P10" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="P10" s="3" t="s">
+      <c r="Q10" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -1338,43 +1373,46 @@
         <v>3100</v>
       </c>
       <c r="E11" t="s">
+        <v>120</v>
+      </c>
+      <c r="F11" t="s">
         <v>39</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>1</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="H11" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="H11">
-        <v>100</v>
-      </c>
       <c r="I11">
+        <v>100</v>
+      </c>
+      <c r="J11">
         <v>2</v>
       </c>
-      <c r="J11" s="7">
+      <c r="K11" s="7">
         <v>3</v>
       </c>
-      <c r="K11" s="7">
+      <c r="L11" s="7">
         <v>4</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>8</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>24</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>14</v>
       </c>
-      <c r="O11" s="6" t="s">
+      <c r="P11" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="P11" s="3" t="s">
+      <c r="Q11" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -1388,43 +1426,46 @@
         <v>3102</v>
       </c>
       <c r="E12" t="s">
+        <v>120</v>
+      </c>
+      <c r="F12" t="s">
         <v>39</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>1</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="H12" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="H12">
-        <v>100</v>
-      </c>
       <c r="I12">
+        <v>100</v>
+      </c>
+      <c r="J12">
         <v>2</v>
       </c>
-      <c r="J12" s="7">
+      <c r="K12" s="7">
         <v>2</v>
       </c>
-      <c r="K12" s="7">
+      <c r="L12" s="7">
         <v>3</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>8</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>24</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>14</v>
       </c>
-      <c r="O12" s="6" t="s">
+      <c r="P12" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="P12" s="3" t="s">
+      <c r="Q12" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>43</v>
       </c>
@@ -1438,43 +1479,46 @@
         <v>3104</v>
       </c>
       <c r="E13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F13" t="s">
         <v>39</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>1</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="H13" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="H13">
-        <v>100</v>
-      </c>
       <c r="I13">
+        <v>100</v>
+      </c>
+      <c r="J13">
         <v>2</v>
       </c>
-      <c r="J13" s="7">
+      <c r="K13" s="7">
         <v>4</v>
       </c>
-      <c r="K13" s="7">
+      <c r="L13" s="7">
         <v>2</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>8</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>24</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>14</v>
       </c>
-      <c r="O13" s="6" t="s">
+      <c r="P13" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="P13" s="3" t="s">
+      <c r="Q13" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>46</v>
       </c>
@@ -1488,43 +1532,46 @@
         <v>3106</v>
       </c>
       <c r="E14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F14" t="s">
         <v>39</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>1</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="H14" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="H14">
-        <v>100</v>
-      </c>
       <c r="I14">
-        <v>2</v>
-      </c>
-      <c r="J14" s="7">
+        <v>100</v>
+      </c>
+      <c r="J14">
         <v>2</v>
       </c>
       <c r="K14" s="7">
         <v>2</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="7">
+        <v>2</v>
+      </c>
+      <c r="M14">
         <v>8</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>24</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>14</v>
       </c>
-      <c r="O14" s="6" t="s">
+      <c r="P14" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>44</v>
       </c>
@@ -1538,43 +1585,46 @@
         <v>3108</v>
       </c>
       <c r="E15" t="s">
+        <v>120</v>
+      </c>
+      <c r="F15" t="s">
         <v>39</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>1</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="H15" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="H15">
-        <v>100</v>
-      </c>
       <c r="I15">
+        <v>100</v>
+      </c>
+      <c r="J15">
         <v>2</v>
       </c>
-      <c r="J15" s="7">
+      <c r="K15" s="7">
         <v>4</v>
       </c>
-      <c r="K15" s="7">
+      <c r="L15" s="7">
         <v>3</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>8</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>24</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>14</v>
       </c>
-      <c r="O15" s="6" t="s">
+      <c r="P15" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="P15" s="3" t="s">
+      <c r="Q15" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>29</v>
       </c>
@@ -1588,43 +1638,46 @@
         <v>3110</v>
       </c>
       <c r="E16" t="s">
+        <v>120</v>
+      </c>
+      <c r="F16" t="s">
         <v>39</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>1</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="H16" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="H16">
-        <v>100</v>
-      </c>
       <c r="I16">
+        <v>100</v>
+      </c>
+      <c r="J16">
         <v>2</v>
       </c>
-      <c r="J16" s="7">
+      <c r="K16" s="7">
         <v>2</v>
       </c>
-      <c r="K16" s="7">
+      <c r="L16" s="7">
         <v>4</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>8</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>24</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>14</v>
       </c>
-      <c r="O16" s="6" t="s">
+      <c r="P16" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="P16" s="3" t="s">
+      <c r="Q16" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>40</v>
       </c>
@@ -1638,43 +1691,46 @@
         <v>3112</v>
       </c>
       <c r="E17" t="s">
+        <v>120</v>
+      </c>
+      <c r="F17" t="s">
         <v>39</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>1</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="H17" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="H17">
-        <v>100</v>
-      </c>
       <c r="I17">
+        <v>100</v>
+      </c>
+      <c r="J17">
         <v>2</v>
       </c>
-      <c r="J17" s="7">
+      <c r="K17" s="7">
         <v>2</v>
       </c>
-      <c r="K17" s="7">
+      <c r="L17" s="7">
         <v>6</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>8</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>24</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>14</v>
       </c>
-      <c r="O17" s="6" t="s">
+      <c r="P17" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="P17" s="3" t="s">
+      <c r="Q17" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>45</v>
       </c>
@@ -1688,46 +1744,49 @@
         <v>3114</v>
       </c>
       <c r="E18" t="s">
+        <v>120</v>
+      </c>
+      <c r="F18" t="s">
         <v>39</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>1</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="H18" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="H18">
-        <v>100</v>
-      </c>
       <c r="I18">
+        <v>100</v>
+      </c>
+      <c r="J18">
         <v>2</v>
-      </c>
-      <c r="J18" s="7">
-        <v>1</v>
       </c>
       <c r="K18" s="7">
         <v>1</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="7">
+        <v>1</v>
+      </c>
+      <c r="M18">
         <v>8</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>24</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>14</v>
       </c>
-      <c r="O18" s="6" t="s">
+      <c r="P18" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="P18" s="3" t="s">
+      <c r="Q18" s="3" t="s">
         <v>48</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>

--- a/Datas/AnimalData.xlsx
+++ b/Datas/AnimalData.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="125">
   <si>
     <t>鸡</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -204,19 +204,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>企鹅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>松鼠</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>野兔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火烈鸟</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -341,15 +333,9 @@
     <t>马</t>
   </si>
   <si>
-    <t>幼鸡,5,0,3000|母鸡,95,301,3001|母鸡,100,0,3001</t>
-  </si>
-  <si>
     <t>幼鸭,5,0,3002|鸭子,95,3007,3003|鸭子,100,0,3003</t>
   </si>
   <si>
-    <t>幼兔,6,0,3004|家兔,114,302,3005|家兔,100,0,3005</t>
-  </si>
-  <si>
     <t>幼绵羊,10,0,3006|绵羊,170,283,3007|绵羊,100,0,3007</t>
   </si>
   <si>
@@ -362,39 +348,102 @@
     <t>幼马,10,0,3013|马,230,276,3012|马,100,0,3012</t>
   </si>
   <si>
-    <t>松鼠,5,0,3100|松鼠,95,235,3100|松鼠,100,0,3100</t>
-  </si>
-  <si>
-    <t>野兔,5,0,3102|野兔,95,302,3102|野兔,100,0,3102</t>
-  </si>
-  <si>
-    <t>火烈鸟,6,0,3104|火烈鸟,174,297,3104|火烈鸟,100,0,3104</t>
-  </si>
-  <si>
-    <t>鹿,10,0,3106|鹿,170,222,3106|鹿,100,0,3106</t>
-  </si>
-  <si>
-    <t>刺猬,6,0,3108|刺猬,174,213,3108|刺猬,100,0,3108</t>
-  </si>
-  <si>
-    <t>大象,20,0,3110|大象,220,240,3110|大象,100,0,3110</t>
-  </si>
-  <si>
-    <t>企鹅,12,0,3112|企鹅,228,260,3112|企鹅,100,0,3112</t>
-  </si>
-  <si>
-    <t>袋鼠,15,0,3114|袋鼠,225,203,3114|袋鼠,100,0,3114</t>
-  </si>
-  <si>
     <t>母鸡</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>家兔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奶牛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>talkId</t>
+  </si>
+  <si>
+    <t>int2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绵羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8100,8101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8102,8103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8104,8104</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8105,8105</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8106,8106</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8107,8107</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8108,8108</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8109,8109</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8110,8110</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8111,8111</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dailyTasks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20,21,22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>鸭子</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>家兔</t>
+    <t>鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兔子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绵羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猪</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -406,86 +455,63 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>talkId</t>
-  </si>
-  <si>
-    <t>int2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>绵羊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>猪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8100,8101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8102,8103</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8104,8104</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8105,8105</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8106,8106</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8107,8107</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8108,8108</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8109,8109</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8110,8110</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8111,8111</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8112,8112</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8113,8113</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8114,8114</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8115,8115</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8116,8116</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dailyTasks</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20,21,22</t>
+    <t>山羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>羊驼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸭子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>企鹅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火烈鸟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼兔,6,0,3004|兔子,114,302,3005|兔子,100,0,3005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小鸡,5,0,3000|母鸡,95,301,3001|母鸡,100,0,3001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>羊驼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼山羊,10,0,3106|山羊,170,241,3106|山羊,100,0,3106</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼火鸡,12,0,3112|火鸡,228,229,3112|火鸡,100,0,3112</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼羊驼,15,0,3114|羊驼,225,203,3114|羊驼,100,0,3114</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -555,7 +581,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -579,10 +605,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -591,6 +613,8 @@
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -871,14 +895,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:Q18"/>
+  <dimension ref="A2:Q13"/>
   <sheetFormatPr defaultColWidth="12.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="6.5" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="7" max="7" width="5.75" customWidth="1"/>
-    <col min="8" max="8" width="19.875" style="9" customWidth="1"/>
-    <col min="9" max="15" width="12.125" customWidth="1"/>
+    <col min="8" max="8" width="19.875" style="7" customWidth="1"/>
+    <col min="9" max="15" width="12.125" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="47.875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -904,8 +928,8 @@
       <c r="G2" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="9" t="s">
-        <v>101</v>
+      <c r="H2" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="I2" t="s">
         <v>23</v>
@@ -949,7 +973,7 @@
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="F3" t="s">
         <v>25</v>
@@ -957,8 +981,8 @@
       <c r="G3" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>100</v>
+      <c r="H3" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="I3" t="s">
         <v>18</v>
@@ -967,10 +991,10 @@
         <v>19</v>
       </c>
       <c r="K3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M3" t="s">
         <v>26</v>
@@ -985,12 +1009,12 @@
         <v>20</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="B4">
         <v>3000</v>
@@ -1002,7 +1026,7 @@
         <v>3000</v>
       </c>
       <c r="E4" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F4" t="s">
         <v>39</v>
@@ -1010,8 +1034,8 @@
       <c r="G4">
         <v>1</v>
       </c>
-      <c r="H4" s="9" t="s">
-        <v>104</v>
+      <c r="H4" s="7" t="s">
+        <v>91</v>
       </c>
       <c r="I4">
         <v>100</v>
@@ -1019,10 +1043,10 @@
       <c r="J4">
         <v>2</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="5">
         <v>2</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="5">
         <v>2</v>
       </c>
       <c r="M4">
@@ -1034,16 +1058,16 @@
       <c r="O4">
         <v>14</v>
       </c>
-      <c r="P4" s="6" t="s">
-        <v>80</v>
+      <c r="P4" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="B5">
         <v>3002</v>
@@ -1055,7 +1079,7 @@
         <v>3002</v>
       </c>
       <c r="E5" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F5" t="s">
         <v>39</v>
@@ -1063,8 +1087,8 @@
       <c r="G5">
         <v>1</v>
       </c>
-      <c r="H5" s="9" t="s">
-        <v>105</v>
+      <c r="H5" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="I5">
         <v>100</v>
@@ -1072,10 +1096,10 @@
       <c r="J5">
         <v>2</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="5">
         <v>1</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="5">
         <v>1</v>
       </c>
       <c r="M5">
@@ -1087,16 +1111,16 @@
       <c r="O5">
         <v>14</v>
       </c>
-      <c r="P5" s="6" t="s">
-        <v>81</v>
+      <c r="P5" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>97</v>
+      <c r="A6" t="s">
+        <v>105</v>
       </c>
       <c r="B6">
         <v>3004</v>
@@ -1108,7 +1132,7 @@
         <v>3004</v>
       </c>
       <c r="E6" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F6" t="s">
         <v>39</v>
@@ -1116,8 +1140,8 @@
       <c r="G6">
         <v>1</v>
       </c>
-      <c r="H6" s="9" t="s">
-        <v>106</v>
+      <c r="H6" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="I6">
         <v>100</v>
@@ -1125,10 +1149,10 @@
       <c r="J6">
         <v>2</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="5">
         <v>2</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="5">
         <v>3</v>
       </c>
       <c r="M6">
@@ -1140,16 +1164,16 @@
       <c r="O6">
         <v>14</v>
       </c>
-      <c r="P6" s="6" t="s">
-        <v>82</v>
+      <c r="P6" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="B7">
         <v>3006</v>
@@ -1161,7 +1185,7 @@
         <v>3006</v>
       </c>
       <c r="E7" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F7" t="s">
         <v>39</v>
@@ -1169,8 +1193,8 @@
       <c r="G7">
         <v>1</v>
       </c>
-      <c r="H7" s="9" t="s">
-        <v>107</v>
+      <c r="H7" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="I7">
         <v>100</v>
@@ -1178,10 +1202,10 @@
       <c r="J7">
         <v>2</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="5">
         <v>7</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="5">
         <v>4</v>
       </c>
       <c r="M7">
@@ -1193,16 +1217,16 @@
       <c r="O7">
         <v>14</v>
       </c>
-      <c r="P7" s="6" t="s">
-        <v>83</v>
+      <c r="P7" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="B8">
         <v>3008</v>
@@ -1214,7 +1238,7 @@
         <v>3008</v>
       </c>
       <c r="E8" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F8" t="s">
         <v>39</v>
@@ -1222,8 +1246,8 @@
       <c r="G8">
         <v>1</v>
       </c>
-      <c r="H8" s="9" t="s">
-        <v>108</v>
+      <c r="H8" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="I8">
         <v>100</v>
@@ -1231,10 +1255,10 @@
       <c r="J8">
         <v>2</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="5">
         <v>4</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="5">
         <v>6</v>
       </c>
       <c r="M8">
@@ -1246,16 +1270,16 @@
       <c r="O8">
         <v>14</v>
       </c>
-      <c r="P8" s="6" t="s">
-        <v>84</v>
+      <c r="P8" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="B9">
         <v>3010</v>
@@ -1267,7 +1291,7 @@
         <v>3010</v>
       </c>
       <c r="E9" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F9" t="s">
         <v>39</v>
@@ -1275,8 +1299,8 @@
       <c r="G9">
         <v>1</v>
       </c>
-      <c r="H9" s="9" t="s">
-        <v>109</v>
+      <c r="H9" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="I9">
         <v>100</v>
@@ -1284,10 +1308,10 @@
       <c r="J9">
         <v>2</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="5">
         <v>4</v>
       </c>
-      <c r="L9" s="7">
+      <c r="L9" s="5">
         <v>4</v>
       </c>
       <c r="M9">
@@ -1299,16 +1323,16 @@
       <c r="O9">
         <v>14</v>
       </c>
-      <c r="P9" s="6" t="s">
-        <v>85</v>
+      <c r="P9" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="B10">
         <v>3012</v>
@@ -1320,7 +1344,7 @@
         <v>3012</v>
       </c>
       <c r="E10" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F10" t="s">
         <v>39</v>
@@ -1328,8 +1352,8 @@
       <c r="G10">
         <v>1</v>
       </c>
-      <c r="H10" s="9" t="s">
-        <v>110</v>
+      <c r="H10" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="I10">
         <v>100</v>
@@ -1337,10 +1361,10 @@
       <c r="J10">
         <v>2</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K10" s="5">
         <v>3</v>
       </c>
-      <c r="L10" s="7">
+      <c r="L10" s="5">
         <v>4</v>
       </c>
       <c r="M10">
@@ -1352,28 +1376,28 @@
       <c r="O10">
         <v>14</v>
       </c>
-      <c r="P10" s="6" t="s">
-        <v>86</v>
+      <c r="P10" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>41</v>
+      <c r="A11" s="9" t="s">
+        <v>118</v>
       </c>
       <c r="B11">
-        <v>3100</v>
+        <v>3014</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>3100</v>
+        <v>3014</v>
       </c>
       <c r="E11" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F11" t="s">
         <v>39</v>
@@ -1381,8 +1405,8 @@
       <c r="G11">
         <v>1</v>
       </c>
-      <c r="H11" s="9" t="s">
-        <v>111</v>
+      <c r="H11" s="7" t="s">
+        <v>98</v>
       </c>
       <c r="I11">
         <v>100</v>
@@ -1390,11 +1414,11 @@
       <c r="J11">
         <v>2</v>
       </c>
-      <c r="K11" s="7">
-        <v>3</v>
-      </c>
-      <c r="L11" s="7">
-        <v>4</v>
+      <c r="K11" s="5">
+        <v>2</v>
+      </c>
+      <c r="L11" s="5">
+        <v>2</v>
       </c>
       <c r="M11">
         <v>8</v>
@@ -1405,28 +1429,28 @@
       <c r="O11">
         <v>14</v>
       </c>
-      <c r="P11" s="6" t="s">
-        <v>87</v>
+      <c r="P11" s="4" t="s">
+        <v>122</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>42</v>
+      <c r="A12" s="9" t="s">
+        <v>120</v>
       </c>
       <c r="B12">
-        <v>3102</v>
+        <v>3016</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>3102</v>
+        <v>3016</v>
       </c>
       <c r="E12" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F12" t="s">
         <v>39</v>
@@ -1434,8 +1458,8 @@
       <c r="G12">
         <v>1</v>
       </c>
-      <c r="H12" s="9" t="s">
-        <v>112</v>
+      <c r="H12" s="7" t="s">
+        <v>99</v>
       </c>
       <c r="I12">
         <v>100</v>
@@ -1443,11 +1467,11 @@
       <c r="J12">
         <v>2</v>
       </c>
-      <c r="K12" s="7">
+      <c r="K12" s="5">
         <v>2</v>
       </c>
-      <c r="L12" s="7">
-        <v>3</v>
+      <c r="L12" s="5">
+        <v>6</v>
       </c>
       <c r="M12">
         <v>8</v>
@@ -1458,28 +1482,28 @@
       <c r="O12">
         <v>14</v>
       </c>
-      <c r="P12" s="6" t="s">
-        <v>88</v>
+      <c r="P12" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>43</v>
+      <c r="A13" s="9" t="s">
+        <v>121</v>
       </c>
       <c r="B13">
-        <v>3104</v>
+        <v>3018</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>3104</v>
+        <v>3018</v>
       </c>
       <c r="E13" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F13" t="s">
         <v>39</v>
@@ -1487,8 +1511,8 @@
       <c r="G13">
         <v>1</v>
       </c>
-      <c r="H13" s="9" t="s">
-        <v>113</v>
+      <c r="H13" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="I13">
         <v>100</v>
@@ -1496,11 +1520,11 @@
       <c r="J13">
         <v>2</v>
       </c>
-      <c r="K13" s="7">
-        <v>4</v>
-      </c>
-      <c r="L13" s="7">
-        <v>2</v>
+      <c r="K13" s="5">
+        <v>1</v>
+      </c>
+      <c r="L13" s="5">
+        <v>1</v>
       </c>
       <c r="M13">
         <v>8</v>
@@ -1511,276 +1535,11 @@
       <c r="O13">
         <v>14</v>
       </c>
-      <c r="P13" s="6" t="s">
-        <v>89</v>
+      <c r="P13" s="4" t="s">
+        <v>124</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B14">
-        <v>3106</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>3106</v>
-      </c>
-      <c r="E14" t="s">
-        <v>120</v>
-      </c>
-      <c r="F14" t="s">
-        <v>39</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="I14">
-        <v>100</v>
-      </c>
-      <c r="J14">
-        <v>2</v>
-      </c>
-      <c r="K14" s="7">
-        <v>2</v>
-      </c>
-      <c r="L14" s="7">
-        <v>2</v>
-      </c>
-      <c r="M14">
-        <v>8</v>
-      </c>
-      <c r="N14">
-        <v>24</v>
-      </c>
-      <c r="O14">
-        <v>14</v>
-      </c>
-      <c r="P14" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15">
-        <v>3108</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>3108</v>
-      </c>
-      <c r="E15" t="s">
-        <v>120</v>
-      </c>
-      <c r="F15" t="s">
-        <v>39</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="I15">
-        <v>100</v>
-      </c>
-      <c r="J15">
-        <v>2</v>
-      </c>
-      <c r="K15" s="7">
-        <v>4</v>
-      </c>
-      <c r="L15" s="7">
-        <v>3</v>
-      </c>
-      <c r="M15">
-        <v>8</v>
-      </c>
-      <c r="N15">
-        <v>24</v>
-      </c>
-      <c r="O15">
-        <v>14</v>
-      </c>
-      <c r="P15" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16">
-        <v>3110</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>3110</v>
-      </c>
-      <c r="E16" t="s">
-        <v>120</v>
-      </c>
-      <c r="F16" t="s">
-        <v>39</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="I16">
-        <v>100</v>
-      </c>
-      <c r="J16">
-        <v>2</v>
-      </c>
-      <c r="K16" s="7">
-        <v>2</v>
-      </c>
-      <c r="L16" s="7">
-        <v>4</v>
-      </c>
-      <c r="M16">
-        <v>8</v>
-      </c>
-      <c r="N16">
-        <v>24</v>
-      </c>
-      <c r="O16">
-        <v>14</v>
-      </c>
-      <c r="P16" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17">
-        <v>3112</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>3112</v>
-      </c>
-      <c r="E17" t="s">
-        <v>120</v>
-      </c>
-      <c r="F17" t="s">
-        <v>39</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="I17">
-        <v>100</v>
-      </c>
-      <c r="J17">
-        <v>2</v>
-      </c>
-      <c r="K17" s="7">
-        <v>2</v>
-      </c>
-      <c r="L17" s="7">
-        <v>6</v>
-      </c>
-      <c r="M17">
-        <v>8</v>
-      </c>
-      <c r="N17">
-        <v>24</v>
-      </c>
-      <c r="O17">
-        <v>14</v>
-      </c>
-      <c r="P17" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" s="3">
-        <v>3114</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18" s="3">
-        <v>3114</v>
-      </c>
-      <c r="E18" t="s">
-        <v>120</v>
-      </c>
-      <c r="F18" t="s">
-        <v>39</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="I18">
-        <v>100</v>
-      </c>
-      <c r="J18">
-        <v>2</v>
-      </c>
-      <c r="K18" s="7">
-        <v>1</v>
-      </c>
-      <c r="L18" s="7">
-        <v>1</v>
-      </c>
-      <c r="M18">
-        <v>8</v>
-      </c>
-      <c r="N18">
-        <v>24</v>
-      </c>
-      <c r="O18">
-        <v>14</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1793,7 +1552,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:X43"/>
+  <dimension ref="A2:X65"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="11" max="11" width="10.75" customWidth="1"/>
@@ -1879,11 +1638,11 @@
       <c r="D14" t="s">
         <v>36</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="5">
         <v>100</v>
       </c>
       <c r="K14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L14">
         <v>5</v>
@@ -1895,9 +1654,9 @@
         <v>3000</v>
       </c>
       <c r="P14" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q14" s="8">
+        <v>71</v>
+      </c>
+      <c r="Q14" s="6">
         <f>I14-L14</f>
         <v>95</v>
       </c>
@@ -1908,7 +1667,7 @@
         <v>3001</v>
       </c>
       <c r="U14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -1930,11 +1689,11 @@
       <c r="D15" t="s">
         <v>36</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="5">
         <v>100</v>
       </c>
       <c r="K15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L15">
         <v>5</v>
@@ -1946,9 +1705,9 @@
         <v>3002</v>
       </c>
       <c r="P15" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q15" s="8">
+        <v>72</v>
+      </c>
+      <c r="Q15" s="6">
         <f t="shared" ref="Q15:Q28" si="0">I15-L15</f>
         <v>95</v>
       </c>
@@ -1959,7 +1718,7 @@
         <v>3003</v>
       </c>
       <c r="U15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="V15">
         <v>100</v>
@@ -1976,16 +1735,16 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
         <v>36</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I16" s="5">
         <v>120</v>
       </c>
       <c r="K16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L16">
         <v>6</v>
@@ -1997,9 +1756,9 @@
         <v>3004</v>
       </c>
       <c r="P16" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q16" s="8">
+        <v>73</v>
+      </c>
+      <c r="Q16" s="6">
         <f t="shared" si="0"/>
         <v>114</v>
       </c>
@@ -2010,7 +1769,7 @@
         <v>3005</v>
       </c>
       <c r="U16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="V16">
         <v>100</v>
@@ -2027,16 +1786,16 @@
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
         <v>36</v>
       </c>
-      <c r="I17" s="7">
+      <c r="I17" s="5">
         <v>180</v>
       </c>
       <c r="K17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L17">
         <v>10</v>
@@ -2048,9 +1807,9 @@
         <v>3006</v>
       </c>
       <c r="P17" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q17" s="8">
+        <v>74</v>
+      </c>
+      <c r="Q17" s="6">
         <f t="shared" si="0"/>
         <v>170</v>
       </c>
@@ -2061,7 +1820,7 @@
         <v>3007</v>
       </c>
       <c r="U17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -2078,19 +1837,19 @@
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
         <v>36</v>
       </c>
       <c r="E18" t="s">
-        <v>49</v>
-      </c>
-      <c r="I18" s="7">
+        <v>47</v>
+      </c>
+      <c r="I18" s="5">
         <v>180</v>
       </c>
       <c r="K18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L18">
         <v>10</v>
@@ -2102,9 +1861,9 @@
         <v>3008</v>
       </c>
       <c r="P18" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q18" s="8">
+        <v>75</v>
+      </c>
+      <c r="Q18" s="6">
         <f t="shared" si="0"/>
         <v>170</v>
       </c>
@@ -2115,7 +1874,7 @@
         <v>3009</v>
       </c>
       <c r="U18" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -2132,16 +1891,16 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
         <v>36</v>
       </c>
-      <c r="I19" s="7">
+      <c r="I19" s="5">
         <v>240</v>
       </c>
       <c r="K19" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L19">
         <v>10</v>
@@ -2153,9 +1912,9 @@
         <v>3010</v>
       </c>
       <c r="P19" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q19" s="8">
+        <v>76</v>
+      </c>
+      <c r="Q19" s="6">
         <f t="shared" si="0"/>
         <v>230</v>
       </c>
@@ -2166,7 +1925,7 @@
         <v>3011</v>
       </c>
       <c r="U19" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -2180,19 +1939,19 @@
     </row>
     <row r="20" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D20" t="s">
         <v>36</v>
       </c>
-      <c r="I20" s="7">
+      <c r="I20" s="5">
         <v>240</v>
       </c>
       <c r="K20" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L20">
         <v>10</v>
@@ -2204,9 +1963,9 @@
         <v>3013</v>
       </c>
       <c r="P20" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q20" s="8">
+        <v>77</v>
+      </c>
+      <c r="Q20" s="6">
         <f t="shared" si="0"/>
         <v>230</v>
       </c>
@@ -2217,7 +1976,7 @@
         <v>3012</v>
       </c>
       <c r="U20" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -2230,11 +1989,11 @@
       </c>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="I21" s="7">
+      <c r="I21" s="5">
         <v>100</v>
       </c>
       <c r="K21" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="L21">
         <v>5</v>
@@ -2246,9 +2005,9 @@
         <v>3100</v>
       </c>
       <c r="P21" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q21" s="8">
+        <v>63</v>
+      </c>
+      <c r="Q21" s="6">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
@@ -2259,7 +2018,7 @@
         <v>3100</v>
       </c>
       <c r="U21" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -2278,11 +2037,11 @@
       <c r="D22" t="s">
         <v>37</v>
       </c>
-      <c r="I22" s="7">
+      <c r="I22" s="5">
         <v>100</v>
       </c>
       <c r="K22" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L22">
         <v>5</v>
@@ -2294,9 +2053,9 @@
         <v>3102</v>
       </c>
       <c r="P22" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q22" s="8">
+        <v>64</v>
+      </c>
+      <c r="Q22" s="6">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
@@ -2307,7 +2066,7 @@
         <v>3102</v>
       </c>
       <c r="U22" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -2326,11 +2085,11 @@
       <c r="D23" t="s">
         <v>37</v>
       </c>
-      <c r="I23" s="7">
+      <c r="I23" s="5">
         <v>180</v>
       </c>
       <c r="K23" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L23">
         <v>6</v>
@@ -2342,9 +2101,9 @@
         <v>3104</v>
       </c>
       <c r="P23" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q23" s="8">
+        <v>65</v>
+      </c>
+      <c r="Q23" s="6">
         <f t="shared" si="0"/>
         <v>174</v>
       </c>
@@ -2355,7 +2114,7 @@
         <v>3104</v>
       </c>
       <c r="U23" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -2374,11 +2133,11 @@
       <c r="D24" t="s">
         <v>37</v>
       </c>
-      <c r="I24" s="7">
+      <c r="I24" s="5">
         <v>180</v>
       </c>
       <c r="K24" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L24">
         <v>10</v>
@@ -2390,9 +2149,9 @@
         <v>3106</v>
       </c>
       <c r="P24" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q24" s="8">
+        <v>66</v>
+      </c>
+      <c r="Q24" s="6">
         <f t="shared" si="0"/>
         <v>170</v>
       </c>
@@ -2403,7 +2162,7 @@
         <v>3106</v>
       </c>
       <c r="U24" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -2422,11 +2181,11 @@
       <c r="D25" t="s">
         <v>37</v>
       </c>
-      <c r="I25" s="7">
+      <c r="I25" s="5">
         <v>180</v>
       </c>
       <c r="K25" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L25">
         <v>6</v>
@@ -2438,9 +2197,9 @@
         <v>3108</v>
       </c>
       <c r="P25" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q25" s="8">
+        <v>67</v>
+      </c>
+      <c r="Q25" s="6">
         <f t="shared" si="0"/>
         <v>174</v>
       </c>
@@ -2451,7 +2210,7 @@
         <v>3108</v>
       </c>
       <c r="U25" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -2470,11 +2229,11 @@
       <c r="D26" t="s">
         <v>37</v>
       </c>
-      <c r="I26" s="7">
+      <c r="I26" s="5">
         <v>240</v>
       </c>
       <c r="K26" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L26">
         <v>20</v>
@@ -2486,9 +2245,9 @@
         <v>3110</v>
       </c>
       <c r="P26" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q26" s="8">
+        <v>68</v>
+      </c>
+      <c r="Q26" s="6">
         <f t="shared" si="0"/>
         <v>220</v>
       </c>
@@ -2499,7 +2258,7 @@
         <v>3110</v>
       </c>
       <c r="U26" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -2518,11 +2277,11 @@
       <c r="D27" t="s">
         <v>37</v>
       </c>
-      <c r="I27" s="7">
+      <c r="I27" s="5">
         <v>240</v>
       </c>
       <c r="K27" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L27">
         <v>12</v>
@@ -2534,9 +2293,9 @@
         <v>3112</v>
       </c>
       <c r="P27" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q27" s="8">
+        <v>69</v>
+      </c>
+      <c r="Q27" s="6">
         <f t="shared" si="0"/>
         <v>228</v>
       </c>
@@ -2547,7 +2306,7 @@
         <v>3112</v>
       </c>
       <c r="U27" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="V27">
         <v>100</v>
@@ -2566,11 +2325,11 @@
       <c r="D28" t="s">
         <v>37</v>
       </c>
-      <c r="I28" s="7">
+      <c r="I28" s="5">
         <v>240</v>
       </c>
       <c r="K28" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L28">
         <v>15</v>
@@ -2582,9 +2341,9 @@
         <v>3114</v>
       </c>
       <c r="P28" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q28" s="8">
+        <v>70</v>
+      </c>
+      <c r="Q28" s="6">
         <f t="shared" si="0"/>
         <v>225</v>
       </c>
@@ -2595,7 +2354,7 @@
         <v>3114</v>
       </c>
       <c r="U28" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -2875,6 +2634,110 @@
       <c r="X43" t="str">
         <f t="shared" si="4"/>
         <v>袋鼠,100,0,3114</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B51" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D51" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B52" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D52" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B53" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D53" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B54" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D54" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B55" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D55" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B56" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D56" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B57" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D57" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B58" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D58" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B59" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D59" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B60" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E60" s="1"/>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B61" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E61" s="1"/>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B63" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B64" s="8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B65" s="3" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
